--- a/data/output/sim_gridrnd/REL2/group_520_60/results/REL2_G9_results_summary.xlsx
+++ b/data/output/sim_gridrnd/REL2/group_520_60/results/REL2_G9_results_summary.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB23"/>
+  <dimension ref="A1:CM23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,24 +436,24 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>mu</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>sigma</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>jnd</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>pse</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>jnd</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>sigma</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>mu</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>n_trials</t>
@@ -466,367 +466,422 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>lat_entropy_100</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_120</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_140</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_160</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_180</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_200</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_40</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_60</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_80</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>model</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>pse_40</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>jnd_40</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>pse_60</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>jnd_60</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>pse_80</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>jnd_80</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>pse_100</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>jnd_100</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>pse_120</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>jnd_120</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>pse_140</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>jnd_140</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>pse_160</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>jnd_160</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>pse_180</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>jnd_180</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>pse_200</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>jnd_200</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_40</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_60</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_80</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_100</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_120</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_140</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_160</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_180</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_200</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_40</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_60</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_80</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_100</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_120</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_140</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_160</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_180</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_200</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_40</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_60</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_80</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_100</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_120</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_140</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_160</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_180</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_200</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_40</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_60</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_80</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_100</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_120</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_140</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_160</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_180</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_200</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_40</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_60</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_80</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_100</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_120</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_140</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_160</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_180</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_200</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_40</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_60</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_80</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_100</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_120</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_140</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_160</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_180</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_200</t>
+        </is>
+      </c>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>pse_est</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>jnd_est</t>
         </is>
       </c>
     </row>
@@ -840,10 +895,10 @@
         <v>518</v>
       </c>
       <c r="C2" t="n">
+        <v>87.47220163083766</v>
+      </c>
+      <c r="D2" t="n">
         <v>59</v>
-      </c>
-      <c r="D2" t="n">
-        <v>87.47220163083766</v>
       </c>
       <c r="E2" t="n">
         <v>518</v>
@@ -852,228 +907,261 @@
         <v>200</v>
       </c>
       <c r="G2" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="H2" t="inlineStr">
+        <v>77.5</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="M2" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I2" t="n">
-        <v>497.9571260173125</v>
-      </c>
-      <c r="J2" t="n">
-        <v>73.71028145905599</v>
-      </c>
-      <c r="K2" t="n">
-        <v>494.252617804937</v>
-      </c>
-      <c r="L2" t="n">
-        <v>80.98923613273615</v>
-      </c>
-      <c r="M2" t="n">
-        <v>495.6533278911261</v>
-      </c>
-      <c r="N2" t="n">
-        <v>80.01975966939352</v>
-      </c>
-      <c r="O2" t="n">
-        <v>493.2452466711423</v>
-      </c>
-      <c r="P2" t="n">
-        <v>86.01552549693865</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>501.1193508260986</v>
-      </c>
       <c r="R2" t="n">
-        <v>88.41791818225232</v>
+        <v>497.96</v>
       </c>
       <c r="S2" t="n">
-        <v>509.4329236486604</v>
+        <v>73.70999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>85.03223826396786</v>
+        <v>494.25</v>
       </c>
       <c r="U2" t="n">
-        <v>513.7985554082614</v>
+        <v>80.98999999999999</v>
       </c>
       <c r="V2" t="n">
-        <v>81.79168105246259</v>
+        <v>495.65</v>
       </c>
       <c r="W2" t="n">
-        <v>515.4276023423378</v>
+        <v>80.02</v>
       </c>
       <c r="X2" t="n">
-        <v>82.01310001598547</v>
+        <v>493.25</v>
       </c>
       <c r="Y2" t="n">
-        <v>513.608609470563</v>
+        <v>86.02</v>
       </c>
       <c r="Z2" t="n">
-        <v>78.8464130537283</v>
+        <v>501.12</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>88.42</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>509.43</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>85.03</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>513.8</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>81.79000000000001</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>515.4299999999999</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>82.01000000000001</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>513.61</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>78.84999999999999</v>
       </c>
       <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS2" t="n">
         <v>499.3</v>
       </c>
-      <c r="AK2" t="n">
+      <c r="AT2" t="n">
         <v>501.25</v>
       </c>
-      <c r="AL2" t="n">
+      <c r="AU2" t="n">
         <v>500.9125</v>
       </c>
-      <c r="AM2" t="n">
+      <c r="AV2" t="n">
         <v>501.27</v>
       </c>
-      <c r="AN2" t="n">
+      <c r="AW2" t="n">
         <v>497.975</v>
       </c>
-      <c r="AO2" t="n">
+      <c r="AX2" t="n">
         <v>498.3071428571429</v>
       </c>
-      <c r="AP2" t="n">
+      <c r="AY2" t="n">
         <v>501.6125</v>
       </c>
-      <c r="AQ2" t="n">
+      <c r="AZ2" t="n">
         <v>504.3444444444444</v>
       </c>
-      <c r="AR2" t="n">
+      <c r="BA2" t="n">
         <v>506.94</v>
       </c>
-      <c r="AS2" t="n">
+      <c r="BB2" t="n">
         <v>84.21258813265389</v>
       </c>
-      <c r="AT2" t="n">
+      <c r="BC2" t="n">
         <v>85.85290229999994</v>
       </c>
-      <c r="AU2" t="n">
+      <c r="BD2" t="n">
         <v>85.32865781055037</v>
       </c>
-      <c r="AV2" t="n">
+      <c r="BE2" t="n">
         <v>85.5511373390208</v>
       </c>
-      <c r="AW2" t="n">
+      <c r="BF2" t="n">
         <v>87.55726340515675</v>
       </c>
-      <c r="AX2" t="n">
+      <c r="BG2" t="n">
         <v>88.6508316316299</v>
       </c>
-      <c r="AY2" t="n">
+      <c r="BH2" t="n">
         <v>87.62455331555192</v>
       </c>
-      <c r="AZ2" t="n">
+      <c r="BI2" t="n">
         <v>85.49212583768704</v>
       </c>
-      <c r="BA2" t="n">
+      <c r="BJ2" t="n">
         <v>83.39392303999135</v>
       </c>
-      <c r="BB2" t="n">
+      <c r="BK2" t="n">
         <v>338</v>
       </c>
-      <c r="BC2" t="n">
+      <c r="BL2" t="n">
         <v>338</v>
       </c>
-      <c r="BD2" t="n">
+      <c r="BM2" t="n">
         <v>338</v>
       </c>
-      <c r="BE2" t="n">
+      <c r="BN2" t="n">
         <v>338</v>
       </c>
-      <c r="BF2" t="n">
+      <c r="BO2" t="n">
         <v>338</v>
       </c>
-      <c r="BG2" t="n">
+      <c r="BP2" t="n">
         <v>338</v>
       </c>
-      <c r="BH2" t="n">
+      <c r="BQ2" t="n">
         <v>338</v>
       </c>
-      <c r="BI2" t="n">
+      <c r="BR2" t="n">
         <v>338</v>
       </c>
-      <c r="BJ2" t="n">
+      <c r="BS2" t="n">
         <v>338</v>
       </c>
-      <c r="BK2" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>669</v>
-      </c>
       <c r="BT2" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC2" t="n">
         <v>0.5555555555555556</v>
       </c>
-      <c r="BU2" t="n">
+      <c r="CD2" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="BV2" t="n">
+      <c r="CE2" t="n">
         <v>0.8571428571428571</v>
       </c>
-      <c r="BW2" t="n">
+      <c r="CF2" t="n">
         <v>0.9444444444444444</v>
       </c>
-      <c r="BX2" t="n">
+      <c r="CG2" t="n">
         <v>0.7826086956521739</v>
       </c>
-      <c r="BY2" t="n">
+      <c r="CH2" t="n">
         <v>0.7142857142857143</v>
       </c>
-      <c r="BZ2" t="n">
+      <c r="CI2" t="n">
         <v>0.7142857142857143</v>
       </c>
-      <c r="CA2" t="n">
+      <c r="CJ2" t="n">
         <v>0.6060606060606061</v>
       </c>
-      <c r="CB2" t="n">
+      <c r="CK2" t="n">
         <v>0.5128205128205128</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>513.61</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>78.84999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -1086,10 +1174,10 @@
         <v>521</v>
       </c>
       <c r="C3" t="n">
+        <v>88.95478131949592</v>
+      </c>
+      <c r="D3" t="n">
         <v>60</v>
-      </c>
-      <c r="D3" t="n">
-        <v>88.95478131949592</v>
       </c>
       <c r="E3" t="n">
         <v>521</v>
@@ -1098,1228 +1186,1393 @@
         <v>200</v>
       </c>
       <c r="G3" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="H3" t="inlineStr">
+        <v>77</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I3" t="n">
-        <v>514.9346088051178</v>
-      </c>
-      <c r="J3" t="n">
-        <v>77.23867247717432</v>
-      </c>
-      <c r="K3" t="n">
-        <v>535.8682082638494</v>
-      </c>
-      <c r="L3" t="n">
-        <v>70.9541659373364</v>
-      </c>
-      <c r="M3" t="n">
-        <v>536.9338770935201</v>
-      </c>
-      <c r="N3" t="n">
-        <v>67.87609710014947</v>
-      </c>
-      <c r="O3" t="n">
-        <v>531.2033669720054</v>
-      </c>
-      <c r="P3" t="n">
-        <v>66.0213132092811</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>522.9738047784566</v>
-      </c>
       <c r="R3" t="n">
-        <v>66.44736999343141</v>
+        <v>514.9299999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>517.5800379207393</v>
+        <v>77.23999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>63.78915725173467</v>
+        <v>535.87</v>
       </c>
       <c r="U3" t="n">
-        <v>511.9056334776924</v>
+        <v>70.95</v>
       </c>
       <c r="V3" t="n">
-        <v>63.66154998618708</v>
+        <v>536.9299999999999</v>
       </c>
       <c r="W3" t="n">
-        <v>509.70275613082</v>
+        <v>67.88</v>
       </c>
       <c r="X3" t="n">
-        <v>68.85324607858904</v>
+        <v>531.2</v>
       </c>
       <c r="Y3" t="n">
-        <v>513.5001976521677</v>
+        <v>66.02</v>
       </c>
       <c r="Z3" t="n">
-        <v>70.61054384343338</v>
+        <v>522.97</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>66.45</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>517.58</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>63.79</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>511.91</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>63.66</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>509.7</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>68.84999999999999</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>513.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>70.61</v>
       </c>
       <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS3" t="n">
         <v>513.975</v>
       </c>
-      <c r="AK3" t="n">
+      <c r="AT3" t="n">
         <v>514.9333333333333</v>
       </c>
-      <c r="AL3" t="n">
+      <c r="AU3" t="n">
         <v>516.5</v>
       </c>
-      <c r="AM3" t="n">
+      <c r="AV3" t="n">
         <v>518.74</v>
       </c>
-      <c r="AN3" t="n">
+      <c r="AW3" t="n">
         <v>518.95</v>
       </c>
-      <c r="AO3" t="n">
+      <c r="AX3" t="n">
         <v>517.2214285714285</v>
       </c>
-      <c r="AP3" t="n">
+      <c r="AY3" t="n">
         <v>514.58125</v>
       </c>
-      <c r="AQ3" t="n">
+      <c r="AZ3" t="n">
         <v>512.5111111111111</v>
       </c>
-      <c r="AR3" t="n">
+      <c r="BA3" t="n">
         <v>511.42</v>
       </c>
-      <c r="AS3" t="n">
+      <c r="BB3" t="n">
         <v>97.77870102941641</v>
       </c>
-      <c r="AT3" t="n">
+      <c r="BC3" t="n">
         <v>93.55833593123715</v>
       </c>
-      <c r="AU3" t="n">
+      <c r="BD3" t="n">
         <v>90.42469242413821</v>
       </c>
-      <c r="AV3" t="n">
+      <c r="BE3" t="n">
         <v>87.36230537251177</v>
       </c>
-      <c r="AW3" t="n">
+      <c r="BF3" t="n">
         <v>84.95811222792872</v>
       </c>
-      <c r="AX3" t="n">
+      <c r="BG3" t="n">
         <v>82.15638987905434</v>
       </c>
-      <c r="AY3" t="n">
+      <c r="BH3" t="n">
         <v>79.29883919981111</v>
       </c>
-      <c r="AZ3" t="n">
+      <c r="BI3" t="n">
         <v>76.66242661383076</v>
       </c>
-      <c r="BA3" t="n">
+      <c r="BJ3" t="n">
         <v>75.25166842004235</v>
       </c>
-      <c r="BB3" t="n">
+      <c r="BK3" t="n">
         <v>337</v>
       </c>
-      <c r="BC3" t="n">
+      <c r="BL3" t="n">
         <v>337</v>
       </c>
-      <c r="BD3" t="n">
+      <c r="BM3" t="n">
         <v>337</v>
       </c>
-      <c r="BE3" t="n">
+      <c r="BN3" t="n">
         <v>337</v>
       </c>
-      <c r="BF3" t="n">
+      <c r="BO3" t="n">
         <v>337</v>
       </c>
-      <c r="BG3" t="n">
+      <c r="BP3" t="n">
         <v>337</v>
       </c>
-      <c r="BH3" t="n">
+      <c r="BQ3" t="n">
         <v>337</v>
       </c>
-      <c r="BI3" t="n">
+      <c r="BR3" t="n">
         <v>337</v>
       </c>
-      <c r="BJ3" t="n">
+      <c r="BS3" t="n">
         <v>337</v>
       </c>
-      <c r="BK3" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>669</v>
-      </c>
       <c r="BT3" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB3" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC3" t="n">
         <v>0.6363636363636364</v>
       </c>
-      <c r="BU3" t="n">
+      <c r="CD3" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="BV3" t="n">
+      <c r="CE3" t="n">
         <v>0.6923076923076923</v>
       </c>
-      <c r="BW3" t="n">
+      <c r="CF3" t="n">
         <v>0.5294117647058824</v>
       </c>
-      <c r="BX3" t="n">
+      <c r="CG3" t="n">
         <v>0.5348837209302325</v>
       </c>
-      <c r="BY3" t="n">
+      <c r="CH3" t="n">
         <v>0.7441860465116279</v>
       </c>
-      <c r="BZ3" t="n">
+      <c r="CI3" t="n">
         <v>0.8604651162790697</v>
       </c>
-      <c r="CA3" t="n">
+      <c r="CJ3" t="n">
         <v>0.9772727272727273</v>
       </c>
-      <c r="CB3" t="n">
+      <c r="CK3" t="n">
         <v>0.8431372549019608</v>
+      </c>
+      <c r="CL3" t="n">
+        <v>513.5</v>
+      </c>
+      <c r="CM3" t="n">
+        <v>70.61</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S04_G9_522_60_REL2</t>
+          <t>S03_G9_521_58_REL2</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C4" t="n">
-        <v>60</v>
+        <v>85.9896219421794</v>
       </c>
       <c r="D4" t="n">
-        <v>88.95478131949592</v>
+        <v>58</v>
       </c>
       <c r="E4" t="n">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F4" t="n">
         <v>200</v>
       </c>
       <c r="G4" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="H4" t="inlineStr">
+        <v>81</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I4" t="n">
-        <v>558.6329057448552</v>
-      </c>
-      <c r="J4" t="n">
-        <v>74.31175683382428</v>
-      </c>
-      <c r="K4" t="n">
-        <v>522.1162327746886</v>
-      </c>
-      <c r="L4" t="n">
-        <v>74.56779064224104</v>
-      </c>
-      <c r="M4" t="n">
-        <v>515.5188995077335</v>
-      </c>
-      <c r="N4" t="n">
-        <v>73.13293560249922</v>
-      </c>
-      <c r="O4" t="n">
-        <v>524.518181290842</v>
-      </c>
-      <c r="P4" t="n">
-        <v>77.52162520443248</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>524.858319852331</v>
-      </c>
       <c r="R4" t="n">
-        <v>76.48921097747501</v>
+        <v>529.12</v>
       </c>
       <c r="S4" t="n">
-        <v>526.3803810722394</v>
+        <v>87.36</v>
       </c>
       <c r="T4" t="n">
-        <v>73.49790253672836</v>
+        <v>514.39</v>
       </c>
       <c r="U4" t="n">
-        <v>525.3753128459147</v>
+        <v>80.78</v>
       </c>
       <c r="V4" t="n">
-        <v>74.89138020213092</v>
+        <v>514.89</v>
       </c>
       <c r="W4" t="n">
-        <v>518.2785224106277</v>
+        <v>73.08</v>
       </c>
       <c r="X4" t="n">
-        <v>74.70333290438714</v>
+        <v>532.66</v>
       </c>
       <c r="Y4" t="n">
-        <v>520.5287435150784</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="Z4" t="n">
-        <v>72.21669794958125</v>
+        <v>541.29</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>78.64</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>536.29</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>84.43000000000001</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>538.1799999999999</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>75.70999999999999</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>526.89</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>76.52</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>529.34</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>74.27</v>
       </c>
       <c r="AJ4" t="n">
-        <v>527.375</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>532.1166666666667</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>528.3375</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>527.13</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>526.9916666666667</v>
+        <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>523.5428571428571</v>
+        <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>523.00625</v>
+        <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>518.5944444444444</v>
+        <v>0</v>
       </c>
       <c r="AR4" t="n">
-        <v>515.9</v>
+        <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>122.2721733470048</v>
+        <v>489.325</v>
       </c>
       <c r="AT4" t="n">
-        <v>109.2886227178088</v>
+        <v>496.3</v>
       </c>
       <c r="AU4" t="n">
-        <v>99.53453467892437</v>
+        <v>500.75</v>
       </c>
       <c r="AV4" t="n">
-        <v>94.15016250649809</v>
+        <v>504.27</v>
       </c>
       <c r="AW4" t="n">
-        <v>91.06513198743463</v>
+        <v>510.625</v>
       </c>
       <c r="AX4" t="n">
-        <v>88.35879545746353</v>
+        <v>516.0642857142857</v>
       </c>
       <c r="AY4" t="n">
-        <v>89.38676474141739</v>
+        <v>520.08125</v>
       </c>
       <c r="AZ4" t="n">
-        <v>88.53572394000201</v>
+        <v>520.2722222222222</v>
       </c>
       <c r="BA4" t="n">
-        <v>88.17386234026499</v>
+        <v>519.83</v>
       </c>
       <c r="BB4" t="n">
-        <v>331</v>
+        <v>120.326303753585</v>
       </c>
       <c r="BC4" t="n">
-        <v>331</v>
+        <v>112.0225126183721</v>
       </c>
       <c r="BD4" t="n">
-        <v>331</v>
+        <v>106.2169360318777</v>
       </c>
       <c r="BE4" t="n">
-        <v>331</v>
+        <v>102.2606331879477</v>
       </c>
       <c r="BF4" t="n">
-        <v>331</v>
+        <v>101.4269082065175</v>
       </c>
       <c r="BG4" t="n">
-        <v>331</v>
+        <v>101.0295721003287</v>
       </c>
       <c r="BH4" t="n">
-        <v>331</v>
+        <v>100.6275913874396</v>
       </c>
       <c r="BI4" t="n">
-        <v>331</v>
+        <v>96.60916856394782</v>
       </c>
       <c r="BJ4" t="n">
-        <v>331</v>
+        <v>93.955527245607</v>
       </c>
       <c r="BK4" t="n">
-        <v>708</v>
+        <v>319</v>
       </c>
       <c r="BL4" t="n">
-        <v>708</v>
+        <v>319</v>
       </c>
       <c r="BM4" t="n">
-        <v>708</v>
+        <v>319</v>
       </c>
       <c r="BN4" t="n">
-        <v>708</v>
+        <v>319</v>
       </c>
       <c r="BO4" t="n">
-        <v>708</v>
+        <v>319</v>
       </c>
       <c r="BP4" t="n">
-        <v>708</v>
+        <v>319</v>
       </c>
       <c r="BQ4" t="n">
-        <v>708</v>
+        <v>319</v>
       </c>
       <c r="BR4" t="n">
-        <v>708</v>
+        <v>319</v>
       </c>
       <c r="BS4" t="n">
-        <v>708</v>
+        <v>319</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.5</v>
+        <v>669</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.8</v>
+        <v>669</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.8333333333333334</v>
+        <v>669</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.7777777777777778</v>
+        <v>669</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.1666666666666667</v>
+        <v>669</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.6538461538461539</v>
+        <v>669</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.6296296296296297</v>
+        <v>669</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.7037037037037037</v>
+        <v>669</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.7407407407407407</v>
+        <v>669</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE4" t="n">
+        <v>0.5789473684210527</v>
+      </c>
+      <c r="CF4" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="CG4" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="CH4" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="CI4" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="CK4" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>529.34</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>74.27</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S03_G9_521_58_REL2</t>
+          <t>S04_G9_522_60_REL2</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C5" t="n">
-        <v>58</v>
+        <v>88.95478131949592</v>
       </c>
       <c r="D5" t="n">
-        <v>85.9896219421794</v>
+        <v>60</v>
       </c>
       <c r="E5" t="n">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="F5" t="n">
         <v>200</v>
       </c>
       <c r="G5" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="H5" t="inlineStr">
+        <v>79.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I5" t="n">
-        <v>529.1181188415195</v>
-      </c>
-      <c r="J5" t="n">
-        <v>87.35664696130195</v>
-      </c>
-      <c r="K5" t="n">
-        <v>514.3946373117302</v>
-      </c>
-      <c r="L5" t="n">
-        <v>80.77991936732109</v>
-      </c>
-      <c r="M5" t="n">
-        <v>514.8856703792441</v>
-      </c>
-      <c r="N5" t="n">
-        <v>73.07789744786949</v>
-      </c>
-      <c r="O5" t="n">
-        <v>532.6567719895262</v>
-      </c>
-      <c r="P5" t="n">
-        <v>78.25634146283211</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>541.2893219180539</v>
-      </c>
       <c r="R5" t="n">
-        <v>78.6354908926257</v>
+        <v>558.63</v>
       </c>
       <c r="S5" t="n">
-        <v>536.2854979686033</v>
+        <v>74.31</v>
       </c>
       <c r="T5" t="n">
-        <v>84.43348442023938</v>
+        <v>522.12</v>
       </c>
       <c r="U5" t="n">
-        <v>538.1824198334884</v>
+        <v>74.56999999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>75.70740867581596</v>
+        <v>515.52</v>
       </c>
       <c r="W5" t="n">
-        <v>526.8908039615383</v>
+        <v>73.13</v>
       </c>
       <c r="X5" t="n">
-        <v>76.52363776789858</v>
+        <v>524.52</v>
       </c>
       <c r="Y5" t="n">
-        <v>529.3425305164624</v>
+        <v>77.52</v>
       </c>
       <c r="Z5" t="n">
-        <v>74.27130791573155</v>
+        <v>524.86</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>76.48999999999999</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>526.38</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>73.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>525.38</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>74.89</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>518.28</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>74.7</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>520.53</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>72.22</v>
       </c>
       <c r="AJ5" t="n">
-        <v>489.325</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>496.3</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>500.75</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>504.27</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>510.625</v>
+        <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>516.0642857142857</v>
+        <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>520.08125</v>
+        <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>520.2722222222222</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>519.83</v>
+        <v>0</v>
       </c>
       <c r="AS5" t="n">
-        <v>120.326303753585</v>
+        <v>527.375</v>
       </c>
       <c r="AT5" t="n">
-        <v>112.0225126183721</v>
+        <v>532.1166666666667</v>
       </c>
       <c r="AU5" t="n">
-        <v>106.2169360318777</v>
+        <v>528.3375</v>
       </c>
       <c r="AV5" t="n">
-        <v>102.2606331879477</v>
+        <v>527.13</v>
       </c>
       <c r="AW5" t="n">
-        <v>101.4269082065175</v>
+        <v>526.9916666666667</v>
       </c>
       <c r="AX5" t="n">
-        <v>101.0295721003287</v>
+        <v>523.5428571428571</v>
       </c>
       <c r="AY5" t="n">
-        <v>100.6275913874396</v>
+        <v>523.00625</v>
       </c>
       <c r="AZ5" t="n">
-        <v>96.60916856394782</v>
+        <v>518.5944444444444</v>
       </c>
       <c r="BA5" t="n">
-        <v>93.955527245607</v>
+        <v>515.9</v>
       </c>
       <c r="BB5" t="n">
-        <v>319</v>
+        <v>122.2721733470048</v>
       </c>
       <c r="BC5" t="n">
-        <v>319</v>
+        <v>109.2886227178088</v>
       </c>
       <c r="BD5" t="n">
-        <v>319</v>
+        <v>99.53453467892437</v>
       </c>
       <c r="BE5" t="n">
-        <v>319</v>
+        <v>94.15016250649809</v>
       </c>
       <c r="BF5" t="n">
-        <v>319</v>
+        <v>91.06513198743463</v>
       </c>
       <c r="BG5" t="n">
-        <v>319</v>
+        <v>88.35879545746353</v>
       </c>
       <c r="BH5" t="n">
-        <v>319</v>
+        <v>89.38676474141739</v>
       </c>
       <c r="BI5" t="n">
-        <v>319</v>
+        <v>88.53572394000201</v>
       </c>
       <c r="BJ5" t="n">
-        <v>319</v>
+        <v>88.17386234026499</v>
       </c>
       <c r="BK5" t="n">
-        <v>669</v>
+        <v>331</v>
       </c>
       <c r="BL5" t="n">
-        <v>669</v>
+        <v>331</v>
       </c>
       <c r="BM5" t="n">
-        <v>669</v>
+        <v>331</v>
       </c>
       <c r="BN5" t="n">
-        <v>669</v>
+        <v>331</v>
       </c>
       <c r="BO5" t="n">
-        <v>669</v>
+        <v>331</v>
       </c>
       <c r="BP5" t="n">
-        <v>669</v>
+        <v>331</v>
       </c>
       <c r="BQ5" t="n">
-        <v>669</v>
+        <v>331</v>
       </c>
       <c r="BR5" t="n">
-        <v>669</v>
+        <v>331</v>
       </c>
       <c r="BS5" t="n">
-        <v>669</v>
+        <v>331</v>
       </c>
       <c r="BT5" t="n">
-        <v>0</v>
+        <v>708</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>708</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.5789473684210527</v>
+        <v>708</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.625</v>
+        <v>708</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.64</v>
+        <v>708</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.76</v>
+        <v>708</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.84</v>
+        <v>708</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.88</v>
+        <v>708</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.64</v>
+        <v>708</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>0.6538461538461539</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>0.6296296296296297</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>0.7037037037037037</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>0.7407407407407407</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>520.53</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>72.22</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S06_G9_519_61_REL2</t>
+          <t>S05_G9_520_59_REL2</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C6" t="n">
-        <v>61</v>
+        <v>87.47220163083766</v>
       </c>
       <c r="D6" t="n">
-        <v>90.43736100815418</v>
+        <v>59</v>
       </c>
       <c r="E6" t="n">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F6" t="n">
         <v>200</v>
       </c>
       <c r="G6" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="H6" t="inlineStr">
+        <v>79.5</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I6" t="n">
-        <v>538.053011857409</v>
-      </c>
-      <c r="J6" t="n">
-        <v>59.19209526241635</v>
-      </c>
-      <c r="K6" t="n">
-        <v>539.7433688896584</v>
-      </c>
-      <c r="L6" t="n">
-        <v>55.44737049249441</v>
-      </c>
-      <c r="M6" t="n">
-        <v>533.9344379251769</v>
-      </c>
-      <c r="N6" t="n">
-        <v>58.1325633910499</v>
-      </c>
-      <c r="O6" t="n">
-        <v>526.3400159530544</v>
-      </c>
-      <c r="P6" t="n">
-        <v>59.27915917281228</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>533.4811794084595</v>
-      </c>
       <c r="R6" t="n">
-        <v>61.73527572832384</v>
+        <v>542.75</v>
       </c>
       <c r="S6" t="n">
-        <v>524.7897226292166</v>
+        <v>38.81</v>
       </c>
       <c r="T6" t="n">
-        <v>62.38578153157435</v>
+        <v>534.9400000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>525.7482888754107</v>
+        <v>46.94</v>
       </c>
       <c r="V6" t="n">
-        <v>57.74903453600471</v>
+        <v>539.29</v>
       </c>
       <c r="W6" t="n">
-        <v>525.6291035045818</v>
+        <v>50.48</v>
       </c>
       <c r="X6" t="n">
-        <v>63.43333849970119</v>
+        <v>532.75</v>
       </c>
       <c r="Y6" t="n">
-        <v>521.1604311349247</v>
+        <v>55.2</v>
       </c>
       <c r="Z6" t="n">
-        <v>61.02166090291396</v>
+        <v>531.5700000000001</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>56.26</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>533.1</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>55.96</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>524.4299999999999</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>58.77</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>523.64</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>55.41</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>525.45</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>56.43</v>
       </c>
       <c r="AJ6" t="n">
-        <v>518.175</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>521.4333333333333</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>524.1625</v>
+        <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>524.45</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>524.3666666666667</v>
+        <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>523.2071428571429</v>
+        <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>522.1875</v>
+        <v>0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>522.5388888888889</v>
+        <v>0</v>
       </c>
       <c r="AR6" t="n">
-        <v>522.795</v>
+        <v>0</v>
       </c>
       <c r="AS6" t="n">
-        <v>85.2006125271409</v>
+        <v>523.85</v>
       </c>
       <c r="AT6" t="n">
-        <v>78.91099768445179</v>
+        <v>527.5333333333333</v>
       </c>
       <c r="AU6" t="n">
-        <v>74.71570178851297</v>
+        <v>530.3125</v>
       </c>
       <c r="AV6" t="n">
-        <v>73.03237295884614</v>
+        <v>530.91</v>
       </c>
       <c r="AW6" t="n">
-        <v>72.21656473567697</v>
+        <v>529.9333333333333</v>
       </c>
       <c r="AX6" t="n">
-        <v>72.85273761191833</v>
+        <v>527.65</v>
       </c>
       <c r="AY6" t="n">
-        <v>73.07634599341979</v>
+        <v>524.31875</v>
       </c>
       <c r="AZ6" t="n">
-        <v>72.13200583258515</v>
+        <v>520.0944444444444</v>
       </c>
       <c r="BA6" t="n">
-        <v>71.18513169897209</v>
+        <v>516.675</v>
       </c>
       <c r="BB6" t="n">
-        <v>333</v>
+        <v>82.18927849786735</v>
       </c>
       <c r="BC6" t="n">
-        <v>333</v>
+        <v>74.05638992611568</v>
       </c>
       <c r="BD6" t="n">
-        <v>333</v>
+        <v>70.18753339269018</v>
       </c>
       <c r="BE6" t="n">
-        <v>333</v>
+        <v>67.20358546982445</v>
       </c>
       <c r="BF6" t="n">
-        <v>333</v>
+        <v>66.36838270006452</v>
       </c>
       <c r="BG6" t="n">
-        <v>333</v>
+        <v>66.56650004748205</v>
       </c>
       <c r="BH6" t="n">
-        <v>333</v>
+        <v>68.07728805143093</v>
       </c>
       <c r="BI6" t="n">
-        <v>333</v>
+        <v>68.99586921791625</v>
       </c>
       <c r="BJ6" t="n">
-        <v>333</v>
+        <v>69.29710942745014</v>
       </c>
       <c r="BK6" t="n">
-        <v>669</v>
+        <v>336</v>
       </c>
       <c r="BL6" t="n">
-        <v>669</v>
+        <v>336</v>
       </c>
       <c r="BM6" t="n">
-        <v>669</v>
+        <v>336</v>
       </c>
       <c r="BN6" t="n">
-        <v>669</v>
+        <v>336</v>
       </c>
       <c r="BO6" t="n">
-        <v>669</v>
+        <v>336</v>
       </c>
       <c r="BP6" t="n">
-        <v>669</v>
+        <v>336</v>
       </c>
       <c r="BQ6" t="n">
-        <v>669</v>
+        <v>336</v>
       </c>
       <c r="BR6" t="n">
-        <v>669</v>
+        <v>336</v>
       </c>
       <c r="BS6" t="n">
-        <v>669</v>
+        <v>336</v>
       </c>
       <c r="BT6" t="n">
-        <v>0.6363636363636364</v>
+        <v>669</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.7142857142857143</v>
+        <v>669</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.5806451612903226</v>
+        <v>669</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.5365853658536586</v>
+        <v>669</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.5098039215686274</v>
+        <v>669</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.4754098360655737</v>
+        <v>669</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.4366197183098591</v>
+        <v>669</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.4320987654320987</v>
+        <v>669</v>
       </c>
       <c r="CB6" t="n">
-        <v>0.4606741573033708</v>
+        <v>669</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>0.7391304347826086</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>0.7878787878787878</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>0.7647058823529411</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>0.7428571428571429</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>0.7428571428571429</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>0.7428571428571429</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>525.45</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>56.43</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S05_G9_520_59_REL2</t>
+          <t>S06_G9_519_61_REL2</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C7" t="n">
-        <v>59</v>
+        <v>90.43736100815418</v>
       </c>
       <c r="D7" t="n">
-        <v>87.47220163083766</v>
+        <v>61</v>
       </c>
       <c r="E7" t="n">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F7" t="n">
         <v>200</v>
       </c>
       <c r="G7" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="H7" t="inlineStr">
+        <v>80</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I7" t="n">
-        <v>542.7532986122121</v>
-      </c>
-      <c r="J7" t="n">
-        <v>38.81174026824908</v>
-      </c>
-      <c r="K7" t="n">
-        <v>534.9365178509418</v>
-      </c>
-      <c r="L7" t="n">
-        <v>46.94013635379007</v>
-      </c>
-      <c r="M7" t="n">
-        <v>539.2900409902186</v>
-      </c>
-      <c r="N7" t="n">
-        <v>50.48022639295323</v>
-      </c>
-      <c r="O7" t="n">
-        <v>532.7489697199036</v>
-      </c>
-      <c r="P7" t="n">
-        <v>55.20380791151072</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>531.5729693712674</v>
-      </c>
       <c r="R7" t="n">
-        <v>56.26176921006464</v>
+        <v>538.05</v>
       </c>
       <c r="S7" t="n">
-        <v>533.1037074888183</v>
+        <v>59.19</v>
       </c>
       <c r="T7" t="n">
-        <v>55.95831130160187</v>
+        <v>539.74</v>
       </c>
       <c r="U7" t="n">
-        <v>524.4284536957476</v>
+        <v>55.45</v>
       </c>
       <c r="V7" t="n">
-        <v>58.77402794028065</v>
+        <v>533.9299999999999</v>
       </c>
       <c r="W7" t="n">
-        <v>523.6441983249606</v>
+        <v>58.13</v>
       </c>
       <c r="X7" t="n">
-        <v>55.40842392175013</v>
+        <v>526.34</v>
       </c>
       <c r="Y7" t="n">
-        <v>525.4532131887967</v>
+        <v>59.28</v>
       </c>
       <c r="Z7" t="n">
-        <v>56.42913191651872</v>
+        <v>533.48</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>61.74</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>524.79</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>62.39</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>525.75</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>57.75</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>525.63</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>63.43</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>521.16</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>61.02</v>
       </c>
       <c r="AJ7" t="n">
-        <v>523.85</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>527.5333333333333</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>530.3125</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>530.91</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>529.9333333333333</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>527.65</v>
+        <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>524.31875</v>
+        <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>520.0944444444444</v>
+        <v>0</v>
       </c>
       <c r="AR7" t="n">
-        <v>516.675</v>
+        <v>0</v>
       </c>
       <c r="AS7" t="n">
-        <v>82.18927849786735</v>
+        <v>518.175</v>
       </c>
       <c r="AT7" t="n">
-        <v>74.05638992611568</v>
+        <v>521.4333333333333</v>
       </c>
       <c r="AU7" t="n">
-        <v>70.18753339269018</v>
+        <v>524.1625</v>
       </c>
       <c r="AV7" t="n">
-        <v>67.20358546982445</v>
+        <v>524.45</v>
       </c>
       <c r="AW7" t="n">
-        <v>66.36838270006452</v>
+        <v>524.3666666666667</v>
       </c>
       <c r="AX7" t="n">
-        <v>66.56650004748205</v>
+        <v>523.2071428571429</v>
       </c>
       <c r="AY7" t="n">
-        <v>68.07728805143093</v>
+        <v>522.1875</v>
       </c>
       <c r="AZ7" t="n">
-        <v>68.99586921791625</v>
+        <v>522.5388888888889</v>
       </c>
       <c r="BA7" t="n">
-        <v>69.29710942745014</v>
+        <v>522.795</v>
       </c>
       <c r="BB7" t="n">
-        <v>336</v>
+        <v>85.2006125271409</v>
       </c>
       <c r="BC7" t="n">
-        <v>336</v>
+        <v>78.91099768445179</v>
       </c>
       <c r="BD7" t="n">
-        <v>336</v>
+        <v>74.71570178851297</v>
       </c>
       <c r="BE7" t="n">
-        <v>336</v>
+        <v>73.03237295884614</v>
       </c>
       <c r="BF7" t="n">
-        <v>336</v>
+        <v>72.21656473567697</v>
       </c>
       <c r="BG7" t="n">
-        <v>336</v>
+        <v>72.85273761191833</v>
       </c>
       <c r="BH7" t="n">
-        <v>336</v>
+        <v>73.07634599341979</v>
       </c>
       <c r="BI7" t="n">
-        <v>336</v>
+        <v>72.13200583258515</v>
       </c>
       <c r="BJ7" t="n">
-        <v>336</v>
+        <v>71.18513169897209</v>
       </c>
       <c r="BK7" t="n">
-        <v>669</v>
+        <v>333</v>
       </c>
       <c r="BL7" t="n">
-        <v>669</v>
+        <v>333</v>
       </c>
       <c r="BM7" t="n">
-        <v>669</v>
+        <v>333</v>
       </c>
       <c r="BN7" t="n">
-        <v>669</v>
+        <v>333</v>
       </c>
       <c r="BO7" t="n">
-        <v>669</v>
+        <v>333</v>
       </c>
       <c r="BP7" t="n">
-        <v>669</v>
+        <v>333</v>
       </c>
       <c r="BQ7" t="n">
-        <v>669</v>
+        <v>333</v>
       </c>
       <c r="BR7" t="n">
-        <v>669</v>
+        <v>333</v>
       </c>
       <c r="BS7" t="n">
-        <v>669</v>
+        <v>333</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.4</v>
+        <v>669</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.9230769230769231</v>
+        <v>669</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.7391304347826086</v>
+        <v>669</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.7857142857142857</v>
+        <v>669</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.7878787878787878</v>
+        <v>669</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.7647058823529411</v>
+        <v>669</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.7428571428571429</v>
+        <v>669</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.7428571428571429</v>
+        <v>669</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.7428571428571429</v>
+        <v>669</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>0.5806451612903226</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>0.5365853658536586</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>0.5098039215686274</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>0.4754098360655737</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>0.4366197183098591</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>0.4320987654320987</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>0.4606741573033708</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>521.16</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>61.02</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S08_G9_519_61_REL2</t>
+          <t>S07_G9_519_61_REL2</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>519</v>
       </c>
       <c r="C8" t="n">
+        <v>90.43736100815418</v>
+      </c>
+      <c r="D8" t="n">
         <v>61</v>
-      </c>
-      <c r="D8" t="n">
-        <v>90.43736100815418</v>
       </c>
       <c r="E8" t="n">
         <v>519</v>
@@ -2328,244 +2581,277 @@
         <v>200</v>
       </c>
       <c r="G8" t="n">
-        <v>0.445</v>
-      </c>
-      <c r="H8" t="inlineStr">
+        <v>82</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I8" t="n">
-        <v>548.0704367483362</v>
-      </c>
-      <c r="J8" t="n">
-        <v>91.32051624357413</v>
-      </c>
-      <c r="K8" t="n">
-        <v>535.9821325064353</v>
-      </c>
-      <c r="L8" t="n">
-        <v>75.82466377724639</v>
-      </c>
-      <c r="M8" t="n">
-        <v>540.7438508766658</v>
-      </c>
-      <c r="N8" t="n">
-        <v>74.24379675179732</v>
-      </c>
-      <c r="O8" t="n">
-        <v>528.7081335577781</v>
-      </c>
-      <c r="P8" t="n">
-        <v>67.37884703320752</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>527.7124338825863</v>
-      </c>
       <c r="R8" t="n">
-        <v>67.68112235246177</v>
+        <v>446.1</v>
       </c>
       <c r="S8" t="n">
-        <v>531.5938548552259</v>
+        <v>80.56999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>64.25015736420781</v>
+        <v>464.01</v>
       </c>
       <c r="U8" t="n">
-        <v>523.9900009366885</v>
+        <v>81.65000000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>61.85129082689256</v>
+        <v>480.25</v>
       </c>
       <c r="W8" t="n">
-        <v>522.98458922434</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="X8" t="n">
-        <v>62.03667575078533</v>
+        <v>485.27</v>
       </c>
       <c r="Y8" t="n">
-        <v>531.092154275494</v>
+        <v>72.02</v>
       </c>
       <c r="Z8" t="n">
-        <v>61.19967566725445</v>
+        <v>486.85</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>76.26000000000001</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>494.58</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>74.13</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>504.49</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>82.23</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>505.03</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>76.97</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>508.42</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>73.97</v>
       </c>
       <c r="AJ8" t="n">
-        <v>534.075</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>535.2</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>534.025</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>530.24</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>526.8083333333333</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>523.45</v>
+        <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>519.575</v>
+        <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>516.7555555555556</v>
+        <v>0</v>
       </c>
       <c r="AR8" t="n">
-        <v>517.3150000000001</v>
+        <v>0</v>
       </c>
       <c r="AS8" t="n">
-        <v>120.7672115062693</v>
+        <v>468.6</v>
       </c>
       <c r="AT8" t="n">
-        <v>115.437544441428</v>
+        <v>464.7666666666667</v>
       </c>
       <c r="AU8" t="n">
-        <v>110.9996593463241</v>
+        <v>465.35</v>
       </c>
       <c r="AV8" t="n">
-        <v>105.4683004508938</v>
+        <v>469.19</v>
       </c>
       <c r="AW8" t="n">
-        <v>100.2275158355008</v>
+        <v>473.2583333333333</v>
       </c>
       <c r="AX8" t="n">
-        <v>96.64887295182051</v>
+        <v>479.6571428571428</v>
       </c>
       <c r="AY8" t="n">
-        <v>92.83052771044663</v>
+        <v>486.575</v>
       </c>
       <c r="AZ8" t="n">
-        <v>89.2197425973411</v>
+        <v>493.2555555555555</v>
       </c>
       <c r="BA8" t="n">
-        <v>86.94846620268812</v>
+        <v>495.925</v>
       </c>
       <c r="BB8" t="n">
-        <v>341</v>
+        <v>102.1757799089393</v>
       </c>
       <c r="BC8" t="n">
-        <v>341</v>
+        <v>98.70804875433861</v>
       </c>
       <c r="BD8" t="n">
-        <v>341</v>
+        <v>95.9153402746401</v>
       </c>
       <c r="BE8" t="n">
-        <v>341</v>
+        <v>92.29785425458168</v>
       </c>
       <c r="BF8" t="n">
-        <v>341</v>
+        <v>89.57729398247204</v>
       </c>
       <c r="BG8" t="n">
-        <v>341</v>
+        <v>88.57101843223012</v>
       </c>
       <c r="BH8" t="n">
-        <v>341</v>
+        <v>89.15594133314953</v>
       </c>
       <c r="BI8" t="n">
-        <v>341</v>
+        <v>91.02399697163027</v>
       </c>
       <c r="BJ8" t="n">
-        <v>341</v>
+        <v>93.93146105006565</v>
       </c>
       <c r="BK8" t="n">
-        <v>706</v>
+        <v>335</v>
       </c>
       <c r="BL8" t="n">
-        <v>706</v>
+        <v>335</v>
       </c>
       <c r="BM8" t="n">
-        <v>706</v>
+        <v>335</v>
       </c>
       <c r="BN8" t="n">
-        <v>706</v>
+        <v>335</v>
       </c>
       <c r="BO8" t="n">
-        <v>706</v>
+        <v>335</v>
       </c>
       <c r="BP8" t="n">
-        <v>706</v>
+        <v>335</v>
       </c>
       <c r="BQ8" t="n">
-        <v>706</v>
+        <v>335</v>
       </c>
       <c r="BR8" t="n">
-        <v>706</v>
+        <v>335</v>
       </c>
       <c r="BS8" t="n">
-        <v>706</v>
+        <v>335</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.7142857142857143</v>
+        <v>669</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.625</v>
+        <v>669</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.7692307692307693</v>
+        <v>669</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.9230769230769231</v>
+        <v>669</v>
       </c>
       <c r="BX8" t="n">
-        <v>1</v>
+        <v>669</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.8666666666666667</v>
+        <v>669</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.7428571428571429</v>
+        <v>669</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.6341463414634146</v>
+        <v>669</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.6341463414634146</v>
+        <v>669</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>0.5769230769230769</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>0.5769230769230769</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>0.7333333333333333</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>0.7333333333333333</v>
+      </c>
+      <c r="CJ8" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>508.42</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>73.97</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S07_G9_519_61_REL2</t>
+          <t>S08_G9_519_61_REL2</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>519</v>
       </c>
       <c r="C9" t="n">
+        <v>90.43736100815418</v>
+      </c>
+      <c r="D9" t="n">
         <v>61</v>
-      </c>
-      <c r="D9" t="n">
-        <v>90.43736100815418</v>
       </c>
       <c r="E9" t="n">
         <v>519</v>
@@ -2574,228 +2860,261 @@
         <v>200</v>
       </c>
       <c r="G9" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="H9" t="inlineStr">
+        <v>83.5</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I9" t="n">
-        <v>446.1025293775147</v>
-      </c>
-      <c r="J9" t="n">
-        <v>80.57459485610521</v>
-      </c>
-      <c r="K9" t="n">
-        <v>464.0052433317585</v>
-      </c>
-      <c r="L9" t="n">
-        <v>81.65048716231689</v>
-      </c>
-      <c r="M9" t="n">
-        <v>480.2505011661576</v>
-      </c>
-      <c r="N9" t="n">
-        <v>76.74194304641965</v>
-      </c>
-      <c r="O9" t="n">
-        <v>485.2673775269619</v>
-      </c>
-      <c r="P9" t="n">
-        <v>72.02262655411349</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>486.849609963799</v>
-      </c>
       <c r="R9" t="n">
-        <v>76.25533243262414</v>
+        <v>548.0700000000001</v>
       </c>
       <c r="S9" t="n">
-        <v>494.5781050493906</v>
+        <v>91.31999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>74.12878671966526</v>
+        <v>535.98</v>
       </c>
       <c r="U9" t="n">
-        <v>504.4890027141855</v>
+        <v>75.81999999999999</v>
       </c>
       <c r="V9" t="n">
-        <v>82.22927350530082</v>
+        <v>540.74</v>
       </c>
       <c r="W9" t="n">
-        <v>505.030385023491</v>
+        <v>74.23999999999999</v>
       </c>
       <c r="X9" t="n">
-        <v>76.97388784103742</v>
+        <v>528.71</v>
       </c>
       <c r="Y9" t="n">
-        <v>508.4244310256502</v>
+        <v>67.38</v>
       </c>
       <c r="Z9" t="n">
-        <v>73.96950339232892</v>
+        <v>527.71</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>67.68000000000001</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>531.59</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>64.25</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>523.99</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>61.85</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>522.98</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>62.04</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>531.09</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>61.2</v>
       </c>
       <c r="AJ9" t="n">
-        <v>468.6</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>464.7666666666667</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>465.35</v>
+        <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>469.19</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>473.2583333333333</v>
+        <v>0</v>
       </c>
       <c r="AO9" t="n">
-        <v>479.6571428571428</v>
+        <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>486.575</v>
+        <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>493.2555555555555</v>
+        <v>0</v>
       </c>
       <c r="AR9" t="n">
-        <v>495.925</v>
+        <v>0</v>
       </c>
       <c r="AS9" t="n">
-        <v>102.1757799089393</v>
+        <v>534.075</v>
       </c>
       <c r="AT9" t="n">
-        <v>98.70804875433861</v>
+        <v>535.2</v>
       </c>
       <c r="AU9" t="n">
-        <v>95.9153402746401</v>
+        <v>534.025</v>
       </c>
       <c r="AV9" t="n">
-        <v>92.29785425458168</v>
+        <v>530.24</v>
       </c>
       <c r="AW9" t="n">
-        <v>89.57729398247204</v>
+        <v>526.8083333333333</v>
       </c>
       <c r="AX9" t="n">
-        <v>88.57101843223012</v>
+        <v>523.45</v>
       </c>
       <c r="AY9" t="n">
-        <v>89.15594133314953</v>
+        <v>519.575</v>
       </c>
       <c r="AZ9" t="n">
-        <v>91.02399697163027</v>
+        <v>516.7555555555556</v>
       </c>
       <c r="BA9" t="n">
-        <v>93.93146105006565</v>
+        <v>517.3150000000001</v>
       </c>
       <c r="BB9" t="n">
-        <v>335</v>
+        <v>120.7672115062693</v>
       </c>
       <c r="BC9" t="n">
-        <v>335</v>
+        <v>115.437544441428</v>
       </c>
       <c r="BD9" t="n">
-        <v>335</v>
+        <v>110.9996593463241</v>
       </c>
       <c r="BE9" t="n">
-        <v>335</v>
+        <v>105.4683004508938</v>
       </c>
       <c r="BF9" t="n">
-        <v>335</v>
+        <v>100.2275158355008</v>
       </c>
       <c r="BG9" t="n">
-        <v>335</v>
+        <v>96.64887295182051</v>
       </c>
       <c r="BH9" t="n">
-        <v>335</v>
+        <v>92.83052771044663</v>
       </c>
       <c r="BI9" t="n">
-        <v>335</v>
+        <v>89.2197425973411</v>
       </c>
       <c r="BJ9" t="n">
-        <v>335</v>
+        <v>86.94846620268812</v>
       </c>
       <c r="BK9" t="n">
-        <v>669</v>
+        <v>341</v>
       </c>
       <c r="BL9" t="n">
-        <v>669</v>
+        <v>341</v>
       </c>
       <c r="BM9" t="n">
-        <v>669</v>
+        <v>341</v>
       </c>
       <c r="BN9" t="n">
-        <v>669</v>
+        <v>341</v>
       </c>
       <c r="BO9" t="n">
-        <v>669</v>
+        <v>341</v>
       </c>
       <c r="BP9" t="n">
-        <v>669</v>
+        <v>341</v>
       </c>
       <c r="BQ9" t="n">
-        <v>669</v>
+        <v>341</v>
       </c>
       <c r="BR9" t="n">
-        <v>669</v>
+        <v>341</v>
       </c>
       <c r="BS9" t="n">
-        <v>669</v>
+        <v>341</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.7272727272727273</v>
+        <v>706</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.65</v>
+        <v>706</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.5769230769230769</v>
+        <v>706</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.5769230769230769</v>
+        <v>706</v>
       </c>
       <c r="BX9" t="n">
-        <v>0</v>
+        <v>706</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.7333333333333333</v>
+        <v>706</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.7333333333333333</v>
+        <v>706</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.9375</v>
+        <v>706</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.8</v>
+        <v>706</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>0.7692307692307693</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>0.7428571428571429</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>0.6341463414634146</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>0.6341463414634146</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>531.09</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>61.2</v>
       </c>
     </row>
     <row r="10">
@@ -2808,10 +3127,10 @@
         <v>521</v>
       </c>
       <c r="C10" t="n">
+        <v>87.47220163083766</v>
+      </c>
+      <c r="D10" t="n">
         <v>59</v>
-      </c>
-      <c r="D10" t="n">
-        <v>87.47220163083766</v>
       </c>
       <c r="E10" t="n">
         <v>521</v>
@@ -2820,228 +3139,261 @@
         <v>200</v>
       </c>
       <c r="G10" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="H10" t="inlineStr">
+        <v>80</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I10" t="n">
-        <v>535.4499785563111</v>
-      </c>
-      <c r="J10" t="n">
-        <v>70.17230218661439</v>
-      </c>
-      <c r="K10" t="n">
-        <v>529.495496573247</v>
-      </c>
-      <c r="L10" t="n">
-        <v>78.39927483483277</v>
-      </c>
-      <c r="M10" t="n">
-        <v>529.3315356667302</v>
-      </c>
-      <c r="N10" t="n">
-        <v>80.54866401128305</v>
-      </c>
-      <c r="O10" t="n">
-        <v>533.4038379109387</v>
-      </c>
-      <c r="P10" t="n">
-        <v>76.63740747351363</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>533.1753261231123</v>
-      </c>
       <c r="R10" t="n">
-        <v>79.98561596574946</v>
+        <v>535.45</v>
       </c>
       <c r="S10" t="n">
-        <v>524.175946647856</v>
+        <v>70.17</v>
       </c>
       <c r="T10" t="n">
-        <v>79.44597062012062</v>
+        <v>529.5</v>
       </c>
       <c r="U10" t="n">
-        <v>529.5761838842947</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="V10" t="n">
-        <v>74.75518605112191</v>
+        <v>529.33</v>
       </c>
       <c r="W10" t="n">
-        <v>533.0293426160694</v>
+        <v>80.55</v>
       </c>
       <c r="X10" t="n">
-        <v>72.47542518776983</v>
+        <v>533.4</v>
       </c>
       <c r="Y10" t="n">
-        <v>529.2604085277646</v>
+        <v>76.64</v>
       </c>
       <c r="Z10" t="n">
-        <v>74.57274298831797</v>
+        <v>533.1799999999999</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>524.1799999999999</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>79.45</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>529.58</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>74.76000000000001</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>533.03</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>72.48</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>529.26</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>74.56999999999999</v>
       </c>
       <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
         <v>534.75</v>
       </c>
-      <c r="AK10" t="n">
+      <c r="AT10" t="n">
         <v>536.0833333333334</v>
       </c>
-      <c r="AL10" t="n">
+      <c r="AU10" t="n">
         <v>534.225</v>
       </c>
-      <c r="AM10" t="n">
+      <c r="AV10" t="n">
         <v>533.17</v>
       </c>
-      <c r="AN10" t="n">
+      <c r="AW10" t="n">
         <v>532.975</v>
       </c>
-      <c r="AO10" t="n">
+      <c r="AX10" t="n">
         <v>529.9071428571428</v>
       </c>
-      <c r="AP10" t="n">
+      <c r="AY10" t="n">
         <v>527.8375</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AZ10" t="n">
         <v>525.9388888888889</v>
       </c>
-      <c r="AR10" t="n">
+      <c r="BA10" t="n">
         <v>522.545</v>
       </c>
-      <c r="AS10" t="n">
+      <c r="BB10" t="n">
         <v>110.6130078245773</v>
       </c>
-      <c r="AT10" t="n">
+      <c r="BC10" t="n">
         <v>102.8019603682515</v>
       </c>
-      <c r="AU10" t="n">
+      <c r="BD10" t="n">
         <v>100.1488860397359</v>
       </c>
-      <c r="AV10" t="n">
+      <c r="BE10" t="n">
         <v>96.5203662446429</v>
       </c>
-      <c r="AW10" t="n">
+      <c r="BF10" t="n">
         <v>93.35857954682045</v>
       </c>
-      <c r="AX10" t="n">
+      <c r="BG10" t="n">
         <v>91.39302071106894</v>
       </c>
-      <c r="AY10" t="n">
+      <c r="BH10" t="n">
         <v>88.18452865298991</v>
       </c>
-      <c r="AZ10" t="n">
+      <c r="BI10" t="n">
         <v>85.36224535530192</v>
       </c>
-      <c r="BA10" t="n">
+      <c r="BJ10" t="n">
         <v>86.37168503045427</v>
       </c>
-      <c r="BB10" t="n">
+      <c r="BK10" t="n">
         <v>317</v>
       </c>
-      <c r="BC10" t="n">
+      <c r="BL10" t="n">
         <v>317</v>
       </c>
-      <c r="BD10" t="n">
+      <c r="BM10" t="n">
         <v>317</v>
       </c>
-      <c r="BE10" t="n">
+      <c r="BN10" t="n">
         <v>317</v>
       </c>
-      <c r="BF10" t="n">
+      <c r="BO10" t="n">
         <v>317</v>
       </c>
-      <c r="BG10" t="n">
+      <c r="BP10" t="n">
         <v>317</v>
       </c>
-      <c r="BH10" t="n">
+      <c r="BQ10" t="n">
         <v>317</v>
       </c>
-      <c r="BI10" t="n">
+      <c r="BR10" t="n">
         <v>317</v>
       </c>
-      <c r="BJ10" t="n">
+      <c r="BS10" t="n">
         <v>317</v>
       </c>
-      <c r="BK10" t="n">
+      <c r="BT10" t="n">
         <v>708</v>
       </c>
-      <c r="BL10" t="n">
+      <c r="BU10" t="n">
         <v>708</v>
       </c>
-      <c r="BM10" t="n">
+      <c r="BV10" t="n">
         <v>708</v>
       </c>
-      <c r="BN10" t="n">
+      <c r="BW10" t="n">
         <v>708</v>
       </c>
-      <c r="BO10" t="n">
+      <c r="BX10" t="n">
         <v>708</v>
       </c>
-      <c r="BP10" t="n">
+      <c r="BY10" t="n">
         <v>708</v>
       </c>
-      <c r="BQ10" t="n">
+      <c r="BZ10" t="n">
         <v>708</v>
       </c>
-      <c r="BR10" t="n">
+      <c r="CA10" t="n">
         <v>708</v>
       </c>
-      <c r="BS10" t="n">
+      <c r="CB10" t="n">
         <v>708</v>
       </c>
-      <c r="BT10" t="n">
+      <c r="CC10" t="n">
         <v>0.8571428571428571</v>
       </c>
-      <c r="BU10" t="n">
+      <c r="CD10" t="n">
         <v>0.7333333333333333</v>
       </c>
-      <c r="BV10" t="n">
+      <c r="CE10" t="n">
         <v>0.68</v>
       </c>
-      <c r="BW10" t="n">
+      <c r="CF10" t="n">
         <v>0.7586206896551724</v>
       </c>
-      <c r="BX10" t="n">
+      <c r="CG10" t="n">
         <v>0.8125</v>
       </c>
-      <c r="BY10" t="n">
+      <c r="CH10" t="n">
         <v>0.9375</v>
       </c>
-      <c r="BZ10" t="n">
+      <c r="CI10" t="n">
         <v>0.9375</v>
       </c>
-      <c r="CA10" t="n">
+      <c r="CJ10" t="n">
         <v>0.9375</v>
       </c>
-      <c r="CB10" t="n">
+      <c r="CK10" t="n">
         <v>0.9375</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>529.26</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>74.56999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -3054,10 +3406,10 @@
         <v>518</v>
       </c>
       <c r="C11" t="n">
+        <v>91.91994069681246</v>
+      </c>
+      <c r="D11" t="n">
         <v>62</v>
-      </c>
-      <c r="D11" t="n">
-        <v>91.91994069681246</v>
       </c>
       <c r="E11" t="n">
         <v>518</v>
@@ -3066,228 +3418,261 @@
         <v>200</v>
       </c>
       <c r="G11" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="H11" t="inlineStr">
+        <v>79</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="Q11" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I11" t="n">
-        <v>509.535405042572</v>
-      </c>
-      <c r="J11" t="n">
-        <v>43.74210141985267</v>
-      </c>
-      <c r="K11" t="n">
-        <v>513.1610401188046</v>
-      </c>
-      <c r="L11" t="n">
-        <v>43.33169049854797</v>
-      </c>
-      <c r="M11" t="n">
-        <v>531.1503127583559</v>
-      </c>
-      <c r="N11" t="n">
-        <v>52.92211588372164</v>
-      </c>
-      <c r="O11" t="n">
-        <v>533.7681043285096</v>
-      </c>
-      <c r="P11" t="n">
-        <v>66.18722545818841</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>526.2589902533729</v>
-      </c>
       <c r="R11" t="n">
-        <v>63.80249549243813</v>
+        <v>509.54</v>
       </c>
       <c r="S11" t="n">
-        <v>531.2394331321583</v>
+        <v>43.74</v>
       </c>
       <c r="T11" t="n">
-        <v>69.12716563198322</v>
+        <v>513.16</v>
       </c>
       <c r="U11" t="n">
-        <v>534.9872879528428</v>
+        <v>43.33</v>
       </c>
       <c r="V11" t="n">
-        <v>66.67152538577891</v>
+        <v>531.15</v>
       </c>
       <c r="W11" t="n">
-        <v>534.0453319107435</v>
+        <v>52.92</v>
       </c>
       <c r="X11" t="n">
-        <v>67.95317471379273</v>
+        <v>533.77</v>
       </c>
       <c r="Y11" t="n">
-        <v>529.4665486792843</v>
+        <v>66.19</v>
       </c>
       <c r="Z11" t="n">
-        <v>65.66565613514871</v>
+        <v>526.26</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>63.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>531.24</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>69.13</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>534.99</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>66.67</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>534.05</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>67.95</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>529.47</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>65.67</v>
       </c>
       <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
         <v>520.25</v>
       </c>
-      <c r="AK11" t="n">
+      <c r="AT11" t="n">
         <v>516.1833333333333</v>
       </c>
-      <c r="AL11" t="n">
+      <c r="AU11" t="n">
         <v>516.9</v>
       </c>
-      <c r="AM11" t="n">
+      <c r="AV11" t="n">
         <v>520.66</v>
       </c>
-      <c r="AN11" t="n">
+      <c r="AW11" t="n">
         <v>520.0083333333333</v>
       </c>
-      <c r="AO11" t="n">
+      <c r="AX11" t="n">
         <v>517.95</v>
       </c>
-      <c r="AP11" t="n">
+      <c r="AY11" t="n">
         <v>517.0625</v>
       </c>
-      <c r="AQ11" t="n">
+      <c r="AZ11" t="n">
         <v>519.8888888888889</v>
       </c>
-      <c r="AR11" t="n">
+      <c r="BA11" t="n">
         <v>520.21</v>
       </c>
-      <c r="AS11" t="n">
+      <c r="BB11" t="n">
         <v>88.83123043164493</v>
       </c>
-      <c r="AT11" t="n">
+      <c r="BC11" t="n">
         <v>76.31349633074232</v>
       </c>
-      <c r="AU11" t="n">
+      <c r="BD11" t="n">
         <v>71.47072827388847</v>
       </c>
-      <c r="AV11" t="n">
+      <c r="BE11" t="n">
         <v>73.41365268122817</v>
       </c>
-      <c r="AW11" t="n">
+      <c r="BF11" t="n">
         <v>76.24658416756925</v>
       </c>
-      <c r="AX11" t="n">
+      <c r="BG11" t="n">
         <v>78.82922998482226</v>
       </c>
-      <c r="AY11" t="n">
+      <c r="BH11" t="n">
         <v>80.1264381696204</v>
       </c>
-      <c r="AZ11" t="n">
+      <c r="BI11" t="n">
         <v>81.30073724477047</v>
       </c>
-      <c r="BA11" t="n">
+      <c r="BJ11" t="n">
         <v>79.07063867201276</v>
       </c>
-      <c r="BB11" t="n">
+      <c r="BK11" t="n">
         <v>336</v>
       </c>
-      <c r="BC11" t="n">
+      <c r="BL11" t="n">
         <v>336</v>
       </c>
-      <c r="BD11" t="n">
+      <c r="BM11" t="n">
         <v>336</v>
       </c>
-      <c r="BE11" t="n">
+      <c r="BN11" t="n">
         <v>336</v>
       </c>
-      <c r="BF11" t="n">
+      <c r="BO11" t="n">
         <v>336</v>
       </c>
-      <c r="BG11" t="n">
+      <c r="BP11" t="n">
         <v>336</v>
       </c>
-      <c r="BH11" t="n">
+      <c r="BQ11" t="n">
         <v>336</v>
       </c>
-      <c r="BI11" t="n">
+      <c r="BR11" t="n">
         <v>336</v>
       </c>
-      <c r="BJ11" t="n">
+      <c r="BS11" t="n">
         <v>336</v>
       </c>
-      <c r="BK11" t="n">
+      <c r="BT11" t="n">
         <v>675</v>
       </c>
-      <c r="BL11" t="n">
+      <c r="BU11" t="n">
         <v>675</v>
       </c>
-      <c r="BM11" t="n">
+      <c r="BV11" t="n">
         <v>675</v>
       </c>
-      <c r="BN11" t="n">
+      <c r="BW11" t="n">
         <v>675</v>
       </c>
-      <c r="BO11" t="n">
+      <c r="BX11" t="n">
         <v>675</v>
       </c>
-      <c r="BP11" t="n">
+      <c r="BY11" t="n">
         <v>675</v>
       </c>
-      <c r="BQ11" t="n">
+      <c r="BZ11" t="n">
         <v>675</v>
       </c>
-      <c r="BR11" t="n">
+      <c r="CA11" t="n">
         <v>675</v>
       </c>
-      <c r="BS11" t="n">
+      <c r="CB11" t="n">
         <v>675</v>
       </c>
-      <c r="BT11" t="n">
+      <c r="CC11" t="n">
         <v>0.7142857142857143</v>
       </c>
-      <c r="BU11" t="n">
+      <c r="CD11" t="n">
         <v>0.9285714285714286</v>
       </c>
-      <c r="BV11" t="n">
+      <c r="CE11" t="n">
         <v>0.9473684210526315</v>
       </c>
-      <c r="BW11" t="n">
+      <c r="CF11" t="n">
         <v>0.75</v>
       </c>
-      <c r="BX11" t="n">
+      <c r="CG11" t="n">
         <v>0.75</v>
       </c>
-      <c r="BY11" t="n">
+      <c r="CH11" t="n">
         <v>0.7916666666666666</v>
       </c>
-      <c r="BZ11" t="n">
+      <c r="CI11" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="CA11" t="n">
+      <c r="CJ11" t="n">
         <v>0.88</v>
       </c>
-      <c r="CB11" t="n">
+      <c r="CK11" t="n">
         <v>0.96</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>529.47</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>65.67</v>
       </c>
     </row>
     <row r="12">
@@ -3300,10 +3685,10 @@
         <v>519</v>
       </c>
       <c r="C12" t="n">
+        <v>88.95478131949592</v>
+      </c>
+      <c r="D12" t="n">
         <v>60</v>
-      </c>
-      <c r="D12" t="n">
-        <v>88.95478131949592</v>
       </c>
       <c r="E12" t="n">
         <v>519</v>
@@ -3312,228 +3697,261 @@
         <v>200</v>
       </c>
       <c r="G12" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="H12" t="inlineStr">
+        <v>77.5</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I12" t="n">
-        <v>550.0993126157298</v>
-      </c>
-      <c r="J12" t="n">
-        <v>66.55829821760425</v>
-      </c>
-      <c r="K12" t="n">
-        <v>520.0720769840943</v>
-      </c>
-      <c r="L12" t="n">
-        <v>68.27792507805735</v>
-      </c>
-      <c r="M12" t="n">
-        <v>516.0868750052596</v>
-      </c>
-      <c r="N12" t="n">
-        <v>66.33615966897169</v>
-      </c>
-      <c r="O12" t="n">
-        <v>510.5295086389453</v>
-      </c>
-      <c r="P12" t="n">
-        <v>67.13140752114886</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>521.8116236738088</v>
-      </c>
       <c r="R12" t="n">
-        <v>71.47868494283206</v>
+        <v>550.1</v>
       </c>
       <c r="S12" t="n">
-        <v>527.2895371620762</v>
+        <v>66.56</v>
       </c>
       <c r="T12" t="n">
-        <v>71.04772850644628</v>
+        <v>520.0700000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>520.8323064941427</v>
+        <v>68.28</v>
       </c>
       <c r="V12" t="n">
-        <v>72.25463219921514</v>
+        <v>516.09</v>
       </c>
       <c r="W12" t="n">
-        <v>522.2229762946105</v>
+        <v>66.34</v>
       </c>
       <c r="X12" t="n">
-        <v>71.89990717493779</v>
+        <v>510.53</v>
       </c>
       <c r="Y12" t="n">
-        <v>521.2486317736774</v>
+        <v>67.13</v>
       </c>
       <c r="Z12" t="n">
-        <v>74.53648930984856</v>
+        <v>521.8099999999999</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>71.48</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>527.29</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>71.05</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>520.83</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>72.25</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>522.22</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>521.25</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>74.54000000000001</v>
       </c>
       <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
         <v>536.375</v>
       </c>
-      <c r="AK12" t="n">
+      <c r="AT12" t="n">
         <v>536.7833333333333</v>
       </c>
-      <c r="AL12" t="n">
+      <c r="AU12" t="n">
         <v>529.35</v>
       </c>
-      <c r="AM12" t="n">
+      <c r="AV12" t="n">
         <v>524.89</v>
       </c>
-      <c r="AN12" t="n">
+      <c r="AW12" t="n">
         <v>522.4666666666667</v>
       </c>
-      <c r="AO12" t="n">
+      <c r="AX12" t="n">
         <v>522.9571428571429</v>
       </c>
-      <c r="AP12" t="n">
+      <c r="AY12" t="n">
         <v>521.53125</v>
       </c>
-      <c r="AQ12" t="n">
+      <c r="AZ12" t="n">
         <v>521.4944444444444</v>
       </c>
-      <c r="AR12" t="n">
+      <c r="BA12" t="n">
         <v>520.73</v>
       </c>
-      <c r="AS12" t="n">
+      <c r="BB12" t="n">
         <v>97.47684019806961</v>
       </c>
-      <c r="AT12" t="n">
+      <c r="BC12" t="n">
         <v>91.46549288605451</v>
       </c>
-      <c r="AU12" t="n">
+      <c r="BD12" t="n">
         <v>87.62421183668359</v>
       </c>
-      <c r="AV12" t="n">
+      <c r="BE12" t="n">
         <v>83.87441743463856</v>
       </c>
-      <c r="AW12" t="n">
+      <c r="BF12" t="n">
         <v>81.57776794091771</v>
       </c>
-      <c r="AX12" t="n">
+      <c r="BG12" t="n">
         <v>80.42493140709996</v>
       </c>
-      <c r="AY12" t="n">
+      <c r="BH12" t="n">
         <v>77.66674979318692</v>
       </c>
-      <c r="AZ12" t="n">
+      <c r="BI12" t="n">
         <v>80.88541258555712</v>
       </c>
-      <c r="BA12" t="n">
+      <c r="BJ12" t="n">
         <v>82.04448244702382</v>
       </c>
-      <c r="BB12" t="n">
+      <c r="BK12" t="n">
         <v>337</v>
       </c>
-      <c r="BC12" t="n">
+      <c r="BL12" t="n">
         <v>337</v>
       </c>
-      <c r="BD12" t="n">
+      <c r="BM12" t="n">
         <v>337</v>
       </c>
-      <c r="BE12" t="n">
+      <c r="BN12" t="n">
         <v>337</v>
       </c>
-      <c r="BF12" t="n">
+      <c r="BO12" t="n">
         <v>337</v>
       </c>
-      <c r="BG12" t="n">
+      <c r="BP12" t="n">
         <v>337</v>
       </c>
-      <c r="BH12" t="n">
+      <c r="BQ12" t="n">
         <v>337</v>
       </c>
-      <c r="BI12" t="n">
+      <c r="BR12" t="n">
         <v>337</v>
       </c>
-      <c r="BJ12" t="n">
+      <c r="BS12" t="n">
         <v>337</v>
       </c>
-      <c r="BK12" t="n">
+      <c r="BT12" t="n">
         <v>675</v>
       </c>
-      <c r="BL12" t="n">
+      <c r="BU12" t="n">
         <v>675</v>
       </c>
-      <c r="BM12" t="n">
+      <c r="BV12" t="n">
         <v>675</v>
       </c>
-      <c r="BN12" t="n">
+      <c r="BW12" t="n">
         <v>675</v>
       </c>
-      <c r="BO12" t="n">
+      <c r="BX12" t="n">
         <v>675</v>
       </c>
-      <c r="BP12" t="n">
+      <c r="BY12" t="n">
         <v>675</v>
       </c>
-      <c r="BQ12" t="n">
+      <c r="BZ12" t="n">
         <v>675</v>
       </c>
-      <c r="BR12" t="n">
+      <c r="CA12" t="n">
         <v>675</v>
       </c>
-      <c r="BS12" t="n">
+      <c r="CB12" t="n">
         <v>675</v>
       </c>
-      <c r="BT12" t="n">
+      <c r="CC12" t="n">
         <v>0.6363636363636364</v>
       </c>
-      <c r="BU12" t="n">
+      <c r="CD12" t="n">
         <v>0.7</v>
       </c>
-      <c r="BV12" t="n">
+      <c r="CE12" t="n">
         <v>0.7</v>
       </c>
-      <c r="BW12" t="n">
+      <c r="CF12" t="n">
         <v>0.9</v>
       </c>
-      <c r="BX12" t="n">
+      <c r="CG12" t="n">
         <v>0.8695652173913043</v>
       </c>
-      <c r="BY12" t="n">
+      <c r="CH12" t="n">
         <v>0.7407407407407407</v>
       </c>
-      <c r="BZ12" t="n">
+      <c r="CI12" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="CA12" t="n">
+      <c r="CJ12" t="n">
         <v>0.6451612903225806</v>
       </c>
-      <c r="CB12" t="n">
+      <c r="CK12" t="n">
         <v>0.6451612903225806</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>521.25</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>74.54000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -3546,10 +3964,10 @@
         <v>519</v>
       </c>
       <c r="C13" t="n">
+        <v>90.43736100815418</v>
+      </c>
+      <c r="D13" t="n">
         <v>61</v>
-      </c>
-      <c r="D13" t="n">
-        <v>90.43736100815418</v>
       </c>
       <c r="E13" t="n">
         <v>519</v>
@@ -3558,228 +3976,261 @@
         <v>200</v>
       </c>
       <c r="G13" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="H13" t="inlineStr">
+        <v>79.5</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="M13" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="Q13" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I13" t="n">
-        <v>547.5903809553035</v>
-      </c>
-      <c r="J13" t="n">
-        <v>66.48087690404994</v>
-      </c>
-      <c r="K13" t="n">
-        <v>542.9358991307726</v>
-      </c>
-      <c r="L13" t="n">
-        <v>62.88872845053693</v>
-      </c>
-      <c r="M13" t="n">
-        <v>531.5568904230398</v>
-      </c>
-      <c r="N13" t="n">
-        <v>61.86722829041697</v>
-      </c>
-      <c r="O13" t="n">
-        <v>535.9212096447122</v>
-      </c>
-      <c r="P13" t="n">
-        <v>64.67448791612684</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>522.5787348866181</v>
-      </c>
       <c r="R13" t="n">
-        <v>64.39923586226554</v>
+        <v>547.59</v>
       </c>
       <c r="S13" t="n">
-        <v>524.5336106700522</v>
+        <v>66.48</v>
       </c>
       <c r="T13" t="n">
-        <v>65.45547076190327</v>
+        <v>542.9400000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>526.458050621017</v>
+        <v>62.89</v>
       </c>
       <c r="V13" t="n">
-        <v>69.65213024063519</v>
+        <v>531.5599999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>530.9392167831027</v>
+        <v>61.87</v>
       </c>
       <c r="X13" t="n">
-        <v>67.19468787312657</v>
+        <v>535.92</v>
       </c>
       <c r="Y13" t="n">
-        <v>532.2538763392456</v>
+        <v>64.67</v>
       </c>
       <c r="Z13" t="n">
-        <v>63.85930717176792</v>
+        <v>522.58</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>524.53</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>526.46</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>530.9400000000001</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>67.19</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>532.25</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>63.86</v>
       </c>
       <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
         <v>543.3</v>
       </c>
-      <c r="AK13" t="n">
+      <c r="AT13" t="n">
         <v>541.5666666666667</v>
       </c>
-      <c r="AL13" t="n">
+      <c r="AU13" t="n">
         <v>539.8375</v>
       </c>
-      <c r="AM13" t="n">
+      <c r="AV13" t="n">
         <v>536.34</v>
       </c>
-      <c r="AN13" t="n">
+      <c r="AW13" t="n">
         <v>534.025</v>
       </c>
-      <c r="AO13" t="n">
+      <c r="AX13" t="n">
         <v>530.2928571428571</v>
       </c>
-      <c r="AP13" t="n">
+      <c r="AY13" t="n">
         <v>529.56875</v>
       </c>
-      <c r="AQ13" t="n">
+      <c r="AZ13" t="n">
         <v>528.4277777777778</v>
       </c>
-      <c r="AR13" t="n">
+      <c r="BA13" t="n">
         <v>528.635</v>
       </c>
-      <c r="AS13" t="n">
+      <c r="BB13" t="n">
         <v>106.9558787538114</v>
       </c>
-      <c r="AT13" t="n">
+      <c r="BC13" t="n">
         <v>94.63321592102615</v>
       </c>
-      <c r="AU13" t="n">
+      <c r="BD13" t="n">
         <v>87.94251584842226</v>
       </c>
-      <c r="AV13" t="n">
+      <c r="BE13" t="n">
         <v>82.96483833528515</v>
       </c>
-      <c r="AW13" t="n">
+      <c r="BF13" t="n">
         <v>79.94690555820991</v>
       </c>
-      <c r="AX13" t="n">
+      <c r="BG13" t="n">
         <v>78.41341871576496</v>
       </c>
-      <c r="AY13" t="n">
+      <c r="BH13" t="n">
         <v>79.92900145402481</v>
       </c>
-      <c r="AZ13" t="n">
+      <c r="BI13" t="n">
         <v>81.09726879601335</v>
       </c>
-      <c r="BA13" t="n">
+      <c r="BJ13" t="n">
         <v>79.73745528294717</v>
       </c>
-      <c r="BB13" t="n">
+      <c r="BK13" t="n">
         <v>316</v>
       </c>
-      <c r="BC13" t="n">
+      <c r="BL13" t="n">
         <v>316</v>
       </c>
-      <c r="BD13" t="n">
+      <c r="BM13" t="n">
         <v>316</v>
       </c>
-      <c r="BE13" t="n">
+      <c r="BN13" t="n">
         <v>316</v>
       </c>
-      <c r="BF13" t="n">
+      <c r="BO13" t="n">
         <v>316</v>
       </c>
-      <c r="BG13" t="n">
+      <c r="BP13" t="n">
         <v>316</v>
       </c>
-      <c r="BH13" t="n">
+      <c r="BQ13" t="n">
         <v>316</v>
       </c>
-      <c r="BI13" t="n">
+      <c r="BR13" t="n">
         <v>316</v>
       </c>
-      <c r="BJ13" t="n">
+      <c r="BS13" t="n">
         <v>316</v>
       </c>
-      <c r="BK13" t="n">
+      <c r="BT13" t="n">
         <v>682</v>
       </c>
-      <c r="BL13" t="n">
+      <c r="BU13" t="n">
         <v>682</v>
       </c>
-      <c r="BM13" t="n">
+      <c r="BV13" t="n">
         <v>682</v>
       </c>
-      <c r="BN13" t="n">
+      <c r="BW13" t="n">
         <v>682</v>
       </c>
-      <c r="BO13" t="n">
+      <c r="BX13" t="n">
         <v>682</v>
       </c>
-      <c r="BP13" t="n">
+      <c r="BY13" t="n">
         <v>682</v>
       </c>
-      <c r="BQ13" t="n">
+      <c r="BZ13" t="n">
         <v>682</v>
       </c>
-      <c r="BR13" t="n">
+      <c r="CA13" t="n">
         <v>682</v>
       </c>
-      <c r="BS13" t="n">
+      <c r="CB13" t="n">
         <v>682</v>
       </c>
-      <c r="BT13" t="n">
+      <c r="CC13" t="n">
         <v>0.6363636363636364</v>
       </c>
-      <c r="BU13" t="n">
+      <c r="CD13" t="n">
         <v>0.7333333333333333</v>
       </c>
-      <c r="BV13" t="n">
+      <c r="CE13" t="n">
         <v>0.5238095238095238</v>
       </c>
-      <c r="BW13" t="n">
+      <c r="CF13" t="n">
         <v>0.4074074074074074</v>
       </c>
-      <c r="BX13" t="n">
+      <c r="CG13" t="n">
         <v>0.5161290322580645</v>
       </c>
-      <c r="BY13" t="n">
+      <c r="CH13" t="n">
         <v>0.53125</v>
       </c>
-      <c r="BZ13" t="n">
+      <c r="CI13" t="n">
         <v>0.59375</v>
       </c>
-      <c r="CA13" t="n">
+      <c r="CJ13" t="n">
         <v>0.59375</v>
       </c>
-      <c r="CB13" t="n">
+      <c r="CK13" t="n">
         <v>0.5277777777777778</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>532.25</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>63.86</v>
       </c>
     </row>
     <row r="14">
@@ -3792,10 +4243,10 @@
         <v>521</v>
       </c>
       <c r="C14" t="n">
+        <v>85.9896219421794</v>
+      </c>
+      <c r="D14" t="n">
         <v>58</v>
-      </c>
-      <c r="D14" t="n">
-        <v>85.9896219421794</v>
       </c>
       <c r="E14" t="n">
         <v>521</v>
@@ -3804,228 +4255,261 @@
         <v>200</v>
       </c>
       <c r="G14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H14" t="inlineStr">
+        <v>78</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Q14" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I14" t="n">
-        <v>559.1886049929286</v>
-      </c>
-      <c r="J14" t="n">
-        <v>68.99111741944894</v>
-      </c>
-      <c r="K14" t="n">
-        <v>558.5821033903785</v>
-      </c>
-      <c r="L14" t="n">
-        <v>96.47993378761527</v>
-      </c>
-      <c r="M14" t="n">
-        <v>572.833095307757</v>
-      </c>
-      <c r="N14" t="n">
-        <v>107.3510993246277</v>
-      </c>
-      <c r="O14" t="n">
-        <v>546.9531258940035</v>
-      </c>
-      <c r="P14" t="n">
-        <v>108.8831783798078</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>546.7831729636238</v>
-      </c>
       <c r="R14" t="n">
-        <v>97.74731597606862</v>
+        <v>559.1900000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>537.4128584216188</v>
+        <v>68.98999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>90.38410585639488</v>
+        <v>558.58</v>
       </c>
       <c r="U14" t="n">
-        <v>541.9257152224428</v>
+        <v>96.48</v>
       </c>
       <c r="V14" t="n">
-        <v>87.24933359688215</v>
+        <v>572.83</v>
       </c>
       <c r="W14" t="n">
-        <v>541.298604620369</v>
+        <v>107.35</v>
       </c>
       <c r="X14" t="n">
-        <v>86.08908944042275</v>
+        <v>546.95</v>
       </c>
       <c r="Y14" t="n">
-        <v>538.4715462775295</v>
+        <v>108.88</v>
       </c>
       <c r="Z14" t="n">
-        <v>86.18262755241977</v>
+        <v>546.78</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>97.75</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>537.41</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>90.38</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>541.9299999999999</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>87.25</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>541.3</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>86.09</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>538.47</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>86.18000000000001</v>
       </c>
       <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
         <v>546.425</v>
       </c>
-      <c r="AK14" t="n">
+      <c r="AT14" t="n">
         <v>550.3666666666667</v>
       </c>
-      <c r="AL14" t="n">
+      <c r="AU14" t="n">
         <v>554.525</v>
       </c>
-      <c r="AM14" t="n">
+      <c r="AV14" t="n">
         <v>556.29</v>
       </c>
-      <c r="AN14" t="n">
+      <c r="AW14" t="n">
         <v>554.4083333333333</v>
       </c>
-      <c r="AO14" t="n">
+      <c r="AX14" t="n">
         <v>550.7428571428571</v>
       </c>
-      <c r="AP14" t="n">
+      <c r="AY14" t="n">
         <v>546.5875</v>
       </c>
-      <c r="AQ14" t="n">
+      <c r="AZ14" t="n">
         <v>543.8166666666667</v>
       </c>
-      <c r="AR14" t="n">
+      <c r="BA14" t="n">
         <v>541.28</v>
       </c>
-      <c r="AS14" t="n">
+      <c r="BB14" t="n">
         <v>119.5298890445398</v>
       </c>
-      <c r="AT14" t="n">
+      <c r="BC14" t="n">
         <v>111.5550636332669</v>
       </c>
-      <c r="AU14" t="n">
+      <c r="BD14" t="n">
         <v>109.7685035654581</v>
       </c>
-      <c r="AV14" t="n">
+      <c r="BE14" t="n">
         <v>108.856630023164</v>
       </c>
-      <c r="AW14" t="n">
+      <c r="BF14" t="n">
         <v>105.793548624458</v>
       </c>
-      <c r="AX14" t="n">
+      <c r="BG14" t="n">
         <v>102.0467239922528</v>
       </c>
-      <c r="AY14" t="n">
+      <c r="BH14" t="n">
         <v>98.28398823689442</v>
       </c>
-      <c r="AZ14" t="n">
+      <c r="BI14" t="n">
         <v>95.23068337230157</v>
       </c>
-      <c r="BA14" t="n">
+      <c r="BJ14" t="n">
         <v>92.50514364077276</v>
       </c>
-      <c r="BB14" t="n">
+      <c r="BK14" t="n">
         <v>326</v>
       </c>
-      <c r="BC14" t="n">
+      <c r="BL14" t="n">
         <v>326</v>
       </c>
-      <c r="BD14" t="n">
+      <c r="BM14" t="n">
         <v>326</v>
       </c>
-      <c r="BE14" t="n">
+      <c r="BN14" t="n">
         <v>326</v>
       </c>
-      <c r="BF14" t="n">
+      <c r="BO14" t="n">
         <v>326</v>
       </c>
-      <c r="BG14" t="n">
+      <c r="BP14" t="n">
         <v>326</v>
       </c>
-      <c r="BH14" t="n">
+      <c r="BQ14" t="n">
         <v>326</v>
       </c>
-      <c r="BI14" t="n">
+      <c r="BR14" t="n">
         <v>326</v>
       </c>
-      <c r="BJ14" t="n">
+      <c r="BS14" t="n">
         <v>326</v>
       </c>
-      <c r="BK14" t="n">
+      <c r="BT14" t="n">
         <v>735</v>
       </c>
-      <c r="BL14" t="n">
+      <c r="BU14" t="n">
         <v>735</v>
       </c>
-      <c r="BM14" t="n">
+      <c r="BV14" t="n">
         <v>735</v>
       </c>
-      <c r="BN14" t="n">
+      <c r="BW14" t="n">
         <v>735</v>
       </c>
-      <c r="BO14" t="n">
+      <c r="BX14" t="n">
         <v>735</v>
       </c>
-      <c r="BP14" t="n">
+      <c r="BY14" t="n">
         <v>735</v>
       </c>
-      <c r="BQ14" t="n">
+      <c r="BZ14" t="n">
         <v>735</v>
       </c>
-      <c r="BR14" t="n">
+      <c r="CA14" t="n">
         <v>735</v>
       </c>
-      <c r="BS14" t="n">
+      <c r="CB14" t="n">
         <v>735</v>
       </c>
-      <c r="BT14" t="n">
+      <c r="CC14" t="n">
         <v>0.7142857142857143</v>
       </c>
-      <c r="BU14" t="n">
+      <c r="CD14" t="n">
         <v>0.7692307692307693</v>
       </c>
-      <c r="BV14" t="n">
+      <c r="CE14" t="n">
         <v>0.8421052631578947</v>
       </c>
-      <c r="BW14" t="n">
+      <c r="CF14" t="n">
         <v>0.9259259259259259</v>
       </c>
-      <c r="BX14" t="n">
+      <c r="CG14" t="n">
         <v>0.7352941176470589</v>
       </c>
-      <c r="BY14" t="n">
+      <c r="CH14" t="n">
         <v>0.6097560975609756</v>
       </c>
-      <c r="BZ14" t="n">
+      <c r="CI14" t="n">
         <v>0.5208333333333334</v>
       </c>
-      <c r="CA14" t="n">
+      <c r="CJ14" t="n">
         <v>0.4310344827586207</v>
       </c>
-      <c r="CB14" t="n">
+      <c r="CK14" t="n">
         <v>0.46875</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>538.47</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>86.18000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -4038,10 +4522,10 @@
         <v>518</v>
       </c>
       <c r="C15" t="n">
+        <v>91.91994069681246</v>
+      </c>
+      <c r="D15" t="n">
         <v>62</v>
-      </c>
-      <c r="D15" t="n">
-        <v>91.91994069681246</v>
       </c>
       <c r="E15" t="n">
         <v>518</v>
@@ -4050,720 +4534,819 @@
         <v>200</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H15" t="inlineStr">
+        <v>83</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Q15" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I15" t="n">
-        <v>564.5866018646815</v>
-      </c>
-      <c r="J15" t="n">
-        <v>108.5086428686595</v>
-      </c>
-      <c r="K15" t="n">
-        <v>550.2584639001598</v>
-      </c>
-      <c r="L15" t="n">
-        <v>101.8588198305749</v>
-      </c>
-      <c r="M15" t="n">
-        <v>565.2772676386304</v>
-      </c>
-      <c r="N15" t="n">
-        <v>91.64727595139736</v>
-      </c>
-      <c r="O15" t="n">
-        <v>544.8070321262375</v>
-      </c>
-      <c r="P15" t="n">
-        <v>87.82127695986541</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>535.8973762210442</v>
-      </c>
       <c r="R15" t="n">
-        <v>88.26178001456073</v>
+        <v>564.59</v>
       </c>
       <c r="S15" t="n">
-        <v>529.5692357093428</v>
+        <v>108.51</v>
       </c>
       <c r="T15" t="n">
-        <v>87.04986409898491</v>
+        <v>550.26</v>
       </c>
       <c r="U15" t="n">
-        <v>526.4205243906076</v>
+        <v>101.86</v>
       </c>
       <c r="V15" t="n">
-        <v>78.97669152463122</v>
+        <v>565.28</v>
       </c>
       <c r="W15" t="n">
-        <v>525.8590301034474</v>
+        <v>91.65000000000001</v>
       </c>
       <c r="X15" t="n">
-        <v>75.65224367030001</v>
+        <v>544.8099999999999</v>
       </c>
       <c r="Y15" t="n">
-        <v>525.2405516798054</v>
+        <v>87.81999999999999</v>
       </c>
       <c r="Z15" t="n">
-        <v>78.62617685725799</v>
+        <v>535.9</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>88.26000000000001</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>529.5700000000001</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>87.05</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>526.42</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>78.98</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>525.86</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>75.65000000000001</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>525.24</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>78.63</v>
       </c>
       <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
         <v>548.85</v>
       </c>
-      <c r="AK15" t="n">
+      <c r="AT15" t="n">
         <v>549.6666666666666</v>
       </c>
-      <c r="AL15" t="n">
+      <c r="AU15" t="n">
         <v>550.5625</v>
       </c>
-      <c r="AM15" t="n">
+      <c r="AV15" t="n">
         <v>549.87</v>
       </c>
-      <c r="AN15" t="n">
+      <c r="AW15" t="n">
         <v>545.425</v>
       </c>
-      <c r="AO15" t="n">
+      <c r="AX15" t="n">
         <v>541.6428571428571</v>
       </c>
-      <c r="AP15" t="n">
+      <c r="AY15" t="n">
         <v>537.9625</v>
       </c>
-      <c r="AQ15" t="n">
+      <c r="AZ15" t="n">
         <v>534.4055555555556</v>
       </c>
-      <c r="AR15" t="n">
+      <c r="BA15" t="n">
         <v>529.4299999999999</v>
       </c>
-      <c r="AS15" t="n">
+      <c r="BB15" t="n">
         <v>137.2937635145894</v>
       </c>
-      <c r="AT15" t="n">
+      <c r="BC15" t="n">
         <v>131.0864430654656</v>
       </c>
-      <c r="AU15" t="n">
+      <c r="BD15" t="n">
         <v>126.0085159572558</v>
       </c>
-      <c r="AV15" t="n">
+      <c r="BE15" t="n">
         <v>119.2126381723012</v>
       </c>
-      <c r="AW15" t="n">
+      <c r="BF15" t="n">
         <v>113.6178288899531</v>
       </c>
-      <c r="AX15" t="n">
+      <c r="BG15" t="n">
         <v>109.0199897416309</v>
       </c>
-      <c r="AY15" t="n">
+      <c r="BH15" t="n">
         <v>104.7710532243997</v>
       </c>
-      <c r="AZ15" t="n">
+      <c r="BI15" t="n">
         <v>101.6991039631794</v>
       </c>
-      <c r="BA15" t="n">
+      <c r="BJ15" t="n">
         <v>100.4351288145736</v>
       </c>
-      <c r="BB15" t="n">
+      <c r="BK15" t="n">
         <v>331</v>
       </c>
-      <c r="BC15" t="n">
+      <c r="BL15" t="n">
         <v>331</v>
       </c>
-      <c r="BD15" t="n">
+      <c r="BM15" t="n">
         <v>331</v>
       </c>
-      <c r="BE15" t="n">
+      <c r="BN15" t="n">
         <v>331</v>
       </c>
-      <c r="BF15" t="n">
+      <c r="BO15" t="n">
         <v>331</v>
       </c>
-      <c r="BG15" t="n">
+      <c r="BP15" t="n">
         <v>331</v>
       </c>
-      <c r="BH15" t="n">
+      <c r="BQ15" t="n">
         <v>331</v>
       </c>
-      <c r="BI15" t="n">
+      <c r="BR15" t="n">
         <v>331</v>
       </c>
-      <c r="BJ15" t="n">
+      <c r="BS15" t="n">
         <v>331</v>
       </c>
-      <c r="BK15" t="n">
+      <c r="BT15" t="n">
         <v>735</v>
       </c>
-      <c r="BL15" t="n">
+      <c r="BU15" t="n">
         <v>735</v>
       </c>
-      <c r="BM15" t="n">
+      <c r="BV15" t="n">
         <v>735</v>
       </c>
-      <c r="BN15" t="n">
+      <c r="BW15" t="n">
         <v>735</v>
       </c>
-      <c r="BO15" t="n">
+      <c r="BX15" t="n">
         <v>735</v>
       </c>
-      <c r="BP15" t="n">
+      <c r="BY15" t="n">
         <v>735</v>
       </c>
-      <c r="BQ15" t="n">
+      <c r="BZ15" t="n">
         <v>735</v>
       </c>
-      <c r="BR15" t="n">
+      <c r="CA15" t="n">
         <v>735</v>
       </c>
-      <c r="BS15" t="n">
+      <c r="CB15" t="n">
         <v>735</v>
       </c>
-      <c r="BT15" t="n">
+      <c r="CC15" t="n">
         <v>0.8125</v>
       </c>
-      <c r="BU15" t="n">
+      <c r="CD15" t="n">
         <v>0.7619047619047619</v>
       </c>
-      <c r="BV15" t="n">
+      <c r="CE15" t="n">
         <v>0.8181818181818182</v>
       </c>
-      <c r="BW15" t="n">
+      <c r="CF15" t="n">
         <v>0.8636363636363636</v>
       </c>
-      <c r="BX15" t="n">
+      <c r="CG15" t="n">
         <v>0.3157894736842105</v>
       </c>
-      <c r="BY15" t="n">
+      <c r="CH15" t="n">
         <v>0.8260869565217391</v>
       </c>
-      <c r="BZ15" t="n">
+      <c r="CI15" t="n">
         <v>0.5789473684210527</v>
       </c>
-      <c r="CA15" t="n">
+      <c r="CJ15" t="n">
         <v>0.8421052631578947</v>
       </c>
-      <c r="CB15" t="n">
+      <c r="CK15" t="n">
         <v>0.7916666666666666</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>525.24</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>78.63</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S16_G9_520_62_REL2</t>
+          <t>S15_G9_521_59_REL2</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C16" t="n">
-        <v>62</v>
+        <v>87.47220163083766</v>
       </c>
       <c r="D16" t="n">
-        <v>91.91994069681246</v>
+        <v>59</v>
       </c>
       <c r="E16" t="n">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F16" t="n">
         <v>200</v>
       </c>
       <c r="G16" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="H16" t="inlineStr">
+        <v>77.5</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="Q16" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I16" t="n">
-        <v>519.4127664812804</v>
-      </c>
-      <c r="J16" t="n">
-        <v>80.33224291332596</v>
-      </c>
-      <c r="K16" t="n">
-        <v>515.8062803614151</v>
-      </c>
-      <c r="L16" t="n">
-        <v>69.92468211467735</v>
-      </c>
-      <c r="M16" t="n">
-        <v>519.6351032954799</v>
-      </c>
-      <c r="N16" t="n">
-        <v>73.60566748884999</v>
-      </c>
-      <c r="O16" t="n">
-        <v>535.863452637972</v>
-      </c>
-      <c r="P16" t="n">
-        <v>72.02339793664066</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>533.3308612277898</v>
-      </c>
       <c r="R16" t="n">
-        <v>68.64270378904396</v>
+        <v>443.43</v>
       </c>
       <c r="S16" t="n">
-        <v>536.6851056055732</v>
+        <v>62.53</v>
       </c>
       <c r="T16" t="n">
-        <v>66.14637734993342</v>
+        <v>487.29</v>
       </c>
       <c r="U16" t="n">
-        <v>533.09344796766</v>
+        <v>69.73</v>
       </c>
       <c r="V16" t="n">
-        <v>68.55724910874248</v>
+        <v>503.09</v>
       </c>
       <c r="W16" t="n">
-        <v>532.5124577107209</v>
+        <v>83.91</v>
       </c>
       <c r="X16" t="n">
-        <v>70.22531602601865</v>
+        <v>509.52</v>
       </c>
       <c r="Y16" t="n">
-        <v>533.7534577571413</v>
+        <v>91.52</v>
       </c>
       <c r="Z16" t="n">
-        <v>71.11122740345283</v>
+        <v>511.32</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>510.2</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>86.77</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>515.98</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>88.19</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>514.14</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>86.48999999999999</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>513.7</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>88.34</v>
       </c>
       <c r="AJ16" t="n">
-        <v>496.125</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>500.1166666666667</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>503.1875</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>507.43</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>512.5583333333333</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>516.1714285714286</v>
+        <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>517.475</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>516.8333333333334</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>515.65</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>104.6086008653208</v>
+        <v>491.475</v>
       </c>
       <c r="AT16" t="n">
-        <v>98.81263273938657</v>
+        <v>482.4833333333333</v>
       </c>
       <c r="AU16" t="n">
-        <v>93.45521571185849</v>
+        <v>487.8125</v>
       </c>
       <c r="AV16" t="n">
-        <v>90.21200086462999</v>
+        <v>492.06</v>
       </c>
       <c r="AW16" t="n">
-        <v>88.59757293828966</v>
+        <v>495.8666666666667</v>
       </c>
       <c r="AX16" t="n">
-        <v>87.09764166539453</v>
+        <v>498.2</v>
       </c>
       <c r="AY16" t="n">
-        <v>86.29092869473592</v>
+        <v>499.9625</v>
       </c>
       <c r="AZ16" t="n">
-        <v>85.38204989600827</v>
+        <v>502.3888888888889</v>
       </c>
       <c r="BA16" t="n">
-        <v>86.32020331301358</v>
+        <v>504.975</v>
       </c>
       <c r="BB16" t="n">
-        <v>336</v>
+        <v>121.6272969978368</v>
       </c>
       <c r="BC16" t="n">
-        <v>336</v>
+        <v>106.9893283878766</v>
       </c>
       <c r="BD16" t="n">
-        <v>336</v>
+        <v>104.9231973576387</v>
       </c>
       <c r="BE16" t="n">
-        <v>336</v>
+        <v>104.237308100315</v>
       </c>
       <c r="BF16" t="n">
-        <v>336</v>
+        <v>104.6691560213524</v>
       </c>
       <c r="BG16" t="n">
-        <v>336</v>
+        <v>103.566486581602</v>
       </c>
       <c r="BH16" t="n">
-        <v>336</v>
+        <v>100.2958677800337</v>
       </c>
       <c r="BI16" t="n">
-        <v>336</v>
+        <v>97.65502711580011</v>
       </c>
       <c r="BJ16" t="n">
-        <v>336</v>
+        <v>95.97475905153397</v>
       </c>
       <c r="BK16" t="n">
-        <v>669</v>
+        <v>344</v>
       </c>
       <c r="BL16" t="n">
-        <v>669</v>
+        <v>344</v>
       </c>
       <c r="BM16" t="n">
-        <v>669</v>
+        <v>344</v>
       </c>
       <c r="BN16" t="n">
-        <v>669</v>
+        <v>344</v>
       </c>
       <c r="BO16" t="n">
-        <v>669</v>
+        <v>344</v>
       </c>
       <c r="BP16" t="n">
-        <v>669</v>
+        <v>344</v>
       </c>
       <c r="BQ16" t="n">
-        <v>669</v>
+        <v>344</v>
       </c>
       <c r="BR16" t="n">
-        <v>669</v>
+        <v>344</v>
       </c>
       <c r="BS16" t="n">
-        <v>669</v>
+        <v>344</v>
       </c>
       <c r="BT16" t="n">
-        <v>0</v>
+        <v>706</v>
       </c>
       <c r="BU16" t="n">
-        <v>0.4117647058823529</v>
+        <v>706</v>
       </c>
       <c r="BV16" t="n">
-        <v>0.5</v>
+        <v>706</v>
       </c>
       <c r="BW16" t="n">
-        <v>0.4137931034482759</v>
+        <v>706</v>
       </c>
       <c r="BX16" t="n">
-        <v>0.4827586206896552</v>
+        <v>706</v>
       </c>
       <c r="BY16" t="n">
-        <v>0.6206896551724138</v>
+        <v>706</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0.6774193548387096</v>
+        <v>706</v>
       </c>
       <c r="CA16" t="n">
-        <v>0.696969696969697</v>
+        <v>706</v>
       </c>
       <c r="CB16" t="n">
-        <v>0.6052631578947368</v>
+        <v>706</v>
+      </c>
+      <c r="CC16" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD16" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="CE16" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="CF16" t="n">
+        <v>0.5217391304347826</v>
+      </c>
+      <c r="CG16" t="n">
+        <v>0.46875</v>
+      </c>
+      <c r="CH16" t="n">
+        <v>0.5142857142857142</v>
+      </c>
+      <c r="CI16" t="n">
+        <v>0.5142857142857142</v>
+      </c>
+      <c r="CJ16" t="n">
+        <v>0.5142857142857142</v>
+      </c>
+      <c r="CK16" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>513.7</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>88.34</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S15_G9_521_59_REL2</t>
+          <t>S16_G9_520_62_REL2</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C17" t="n">
-        <v>59</v>
+        <v>91.91994069681246</v>
       </c>
       <c r="D17" t="n">
-        <v>87.47220163083766</v>
+        <v>62</v>
       </c>
       <c r="E17" t="n">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F17" t="n">
         <v>200</v>
       </c>
       <c r="G17" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="H17" t="inlineStr">
+        <v>80.5</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="M17" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q17" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I17" t="n">
-        <v>443.4267803905593</v>
-      </c>
-      <c r="J17" t="n">
-        <v>62.53136460152098</v>
-      </c>
-      <c r="K17" t="n">
-        <v>487.2938835394391</v>
-      </c>
-      <c r="L17" t="n">
-        <v>69.72988708260085</v>
-      </c>
-      <c r="M17" t="n">
-        <v>503.0864158294987</v>
-      </c>
-      <c r="N17" t="n">
-        <v>83.9091995123359</v>
-      </c>
-      <c r="O17" t="n">
-        <v>509.5245596731526</v>
-      </c>
-      <c r="P17" t="n">
-        <v>91.51611417851311</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>511.3199990019357</v>
-      </c>
       <c r="R17" t="n">
-        <v>99.99806515909133</v>
+        <v>519.41</v>
       </c>
       <c r="S17" t="n">
-        <v>510.1951450016931</v>
+        <v>80.33</v>
       </c>
       <c r="T17" t="n">
-        <v>86.77111569273835</v>
+        <v>515.8099999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>515.981275944871</v>
+        <v>69.92</v>
       </c>
       <c r="V17" t="n">
-        <v>88.19399135656724</v>
+        <v>519.64</v>
       </c>
       <c r="W17" t="n">
-        <v>514.1412442214125</v>
+        <v>73.61</v>
       </c>
       <c r="X17" t="n">
-        <v>86.48734433244208</v>
+        <v>535.86</v>
       </c>
       <c r="Y17" t="n">
-        <v>513.6964481015809</v>
+        <v>72.02</v>
       </c>
       <c r="Z17" t="n">
-        <v>88.33740163444622</v>
+        <v>533.33</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>68.64</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>536.6900000000001</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>66.15000000000001</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>533.09</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>68.56</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>532.51</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>70.23</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>533.75</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>71.11</v>
       </c>
       <c r="AJ17" t="n">
-        <v>491.475</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>482.4833333333333</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>487.8125</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>492.06</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>495.8666666666667</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
-        <v>498.2</v>
+        <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>499.9625</v>
+        <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>502.3888888888889</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>504.975</v>
+        <v>0</v>
       </c>
       <c r="AS17" t="n">
-        <v>121.6272969978368</v>
+        <v>496.125</v>
       </c>
       <c r="AT17" t="n">
-        <v>106.9893283878766</v>
+        <v>500.1166666666667</v>
       </c>
       <c r="AU17" t="n">
-        <v>104.9231973576387</v>
+        <v>503.1875</v>
       </c>
       <c r="AV17" t="n">
-        <v>104.237308100315</v>
+        <v>507.43</v>
       </c>
       <c r="AW17" t="n">
-        <v>104.6691560213524</v>
+        <v>512.5583333333333</v>
       </c>
       <c r="AX17" t="n">
-        <v>103.566486581602</v>
+        <v>516.1714285714286</v>
       </c>
       <c r="AY17" t="n">
-        <v>100.2958677800337</v>
+        <v>517.475</v>
       </c>
       <c r="AZ17" t="n">
-        <v>97.65502711580011</v>
+        <v>516.8333333333334</v>
       </c>
       <c r="BA17" t="n">
-        <v>95.97475905153397</v>
+        <v>515.65</v>
       </c>
       <c r="BB17" t="n">
-        <v>344</v>
+        <v>104.6086008653208</v>
       </c>
       <c r="BC17" t="n">
-        <v>344</v>
+        <v>98.81263273938657</v>
       </c>
       <c r="BD17" t="n">
-        <v>344</v>
+        <v>93.45521571185849</v>
       </c>
       <c r="BE17" t="n">
-        <v>344</v>
+        <v>90.21200086462999</v>
       </c>
       <c r="BF17" t="n">
-        <v>344</v>
+        <v>88.59757293828966</v>
       </c>
       <c r="BG17" t="n">
-        <v>344</v>
+        <v>87.09764166539453</v>
       </c>
       <c r="BH17" t="n">
-        <v>344</v>
+        <v>86.29092869473592</v>
       </c>
       <c r="BI17" t="n">
-        <v>344</v>
+        <v>85.38204989600827</v>
       </c>
       <c r="BJ17" t="n">
-        <v>344</v>
+        <v>86.32020331301358</v>
       </c>
       <c r="BK17" t="n">
-        <v>706</v>
+        <v>336</v>
       </c>
       <c r="BL17" t="n">
-        <v>706</v>
+        <v>336</v>
       </c>
       <c r="BM17" t="n">
-        <v>706</v>
+        <v>336</v>
       </c>
       <c r="BN17" t="n">
-        <v>706</v>
+        <v>336</v>
       </c>
       <c r="BO17" t="n">
-        <v>706</v>
+        <v>336</v>
       </c>
       <c r="BP17" t="n">
-        <v>706</v>
+        <v>336</v>
       </c>
       <c r="BQ17" t="n">
-        <v>706</v>
+        <v>336</v>
       </c>
       <c r="BR17" t="n">
-        <v>706</v>
+        <v>336</v>
       </c>
       <c r="BS17" t="n">
-        <v>706</v>
+        <v>336</v>
       </c>
       <c r="BT17" t="n">
-        <v>1</v>
+        <v>669</v>
       </c>
       <c r="BU17" t="n">
-        <v>0.9</v>
+        <v>669</v>
       </c>
       <c r="BV17" t="n">
-        <v>0.625</v>
+        <v>669</v>
       </c>
       <c r="BW17" t="n">
-        <v>0.5217391304347826</v>
+        <v>669</v>
       </c>
       <c r="BX17" t="n">
-        <v>0.46875</v>
+        <v>669</v>
       </c>
       <c r="BY17" t="n">
-        <v>0.5142857142857142</v>
+        <v>669</v>
       </c>
       <c r="BZ17" t="n">
-        <v>0.5142857142857142</v>
+        <v>669</v>
       </c>
       <c r="CA17" t="n">
-        <v>0.5142857142857142</v>
+        <v>669</v>
       </c>
       <c r="CB17" t="n">
-        <v>0.5714285714285714</v>
+        <v>669</v>
+      </c>
+      <c r="CC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD17" t="n">
+        <v>0.4117647058823529</v>
+      </c>
+      <c r="CE17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="CF17" t="n">
+        <v>0.4137931034482759</v>
+      </c>
+      <c r="CG17" t="n">
+        <v>0.4827586206896552</v>
+      </c>
+      <c r="CH17" t="n">
+        <v>0.6206896551724138</v>
+      </c>
+      <c r="CI17" t="n">
+        <v>0.6774193548387096</v>
+      </c>
+      <c r="CJ17" t="n">
+        <v>0.696969696969697</v>
+      </c>
+      <c r="CK17" t="n">
+        <v>0.6052631578947368</v>
+      </c>
+      <c r="CL17" t="n">
+        <v>533.75</v>
+      </c>
+      <c r="CM17" t="n">
+        <v>71.11</v>
       </c>
     </row>
     <row r="18">
@@ -4776,10 +5359,10 @@
         <v>520</v>
       </c>
       <c r="C18" t="n">
+        <v>88.95478131949592</v>
+      </c>
+      <c r="D18" t="n">
         <v>60</v>
-      </c>
-      <c r="D18" t="n">
-        <v>88.95478131949592</v>
       </c>
       <c r="E18" t="n">
         <v>520</v>
@@ -4788,228 +5371,261 @@
         <v>200</v>
       </c>
       <c r="G18" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="H18" t="inlineStr">
+        <v>79.5</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q18" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I18" t="n">
-        <v>514.0688648006288</v>
-      </c>
-      <c r="J18" t="n">
-        <v>78.59793838700465</v>
-      </c>
-      <c r="K18" t="n">
-        <v>493.9166204706708</v>
-      </c>
-      <c r="L18" t="n">
-        <v>81.72099203712621</v>
-      </c>
-      <c r="M18" t="n">
-        <v>487.9771687879323</v>
-      </c>
-      <c r="N18" t="n">
-        <v>77.95955688914951</v>
-      </c>
-      <c r="O18" t="n">
-        <v>488.384047232359</v>
-      </c>
-      <c r="P18" t="n">
-        <v>78.40109505552942</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>494.8070943853423</v>
-      </c>
       <c r="R18" t="n">
-        <v>84.78276528098277</v>
+        <v>514.0700000000001</v>
       </c>
       <c r="S18" t="n">
-        <v>496.8057473706282</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>82.18506620241286</v>
+        <v>493.92</v>
       </c>
       <c r="U18" t="n">
-        <v>501.5048592511851</v>
+        <v>81.72</v>
       </c>
       <c r="V18" t="n">
-        <v>86.21960288875158</v>
+        <v>487.98</v>
       </c>
       <c r="W18" t="n">
-        <v>500.609325810372</v>
+        <v>77.95999999999999</v>
       </c>
       <c r="X18" t="n">
-        <v>81.58665874245543</v>
+        <v>488.38</v>
       </c>
       <c r="Y18" t="n">
-        <v>499.1127462843546</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="Z18" t="n">
-        <v>83.13151687146164</v>
+        <v>494.81</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>84.78</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>496.81</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>82.19</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>501.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>86.22</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>500.61</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>81.59</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>499.11</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>83.13</v>
       </c>
       <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
         <v>492.7</v>
       </c>
-      <c r="AK18" t="n">
+      <c r="AT18" t="n">
         <v>493.8</v>
       </c>
-      <c r="AL18" t="n">
+      <c r="AU18" t="n">
         <v>493.0625</v>
       </c>
-      <c r="AM18" t="n">
+      <c r="AV18" t="n">
         <v>492.39</v>
       </c>
-      <c r="AN18" t="n">
+      <c r="AW18" t="n">
         <v>491.3666666666667</v>
       </c>
-      <c r="AO18" t="n">
+      <c r="AX18" t="n">
         <v>490.9642857142857</v>
       </c>
-      <c r="AP18" t="n">
+      <c r="AY18" t="n">
         <v>491.3</v>
       </c>
-      <c r="AQ18" t="n">
+      <c r="AZ18" t="n">
         <v>491.6166666666667</v>
       </c>
-      <c r="AR18" t="n">
+      <c r="BA18" t="n">
         <v>492.985</v>
       </c>
-      <c r="AS18" t="n">
+      <c r="BB18" t="n">
         <v>100.2863899041141</v>
       </c>
-      <c r="AT18" t="n">
+      <c r="BC18" t="n">
         <v>96.93465152702962</v>
       </c>
-      <c r="AU18" t="n">
+      <c r="BD18" t="n">
         <v>95.11996947933699</v>
       </c>
-      <c r="AV18" t="n">
+      <c r="BE18" t="n">
         <v>93.76181472219915</v>
       </c>
-      <c r="AW18" t="n">
+      <c r="BF18" t="n">
         <v>92.95580789935732</v>
       </c>
-      <c r="AX18" t="n">
+      <c r="BG18" t="n">
         <v>92.37195080714906</v>
       </c>
-      <c r="AY18" t="n">
+      <c r="BH18" t="n">
         <v>91.60552658000499</v>
       </c>
-      <c r="AZ18" t="n">
+      <c r="BI18" t="n">
         <v>90.99818526884052</v>
       </c>
-      <c r="BA18" t="n">
+      <c r="BJ18" t="n">
         <v>90.66551039397507</v>
       </c>
-      <c r="BB18" t="n">
+      <c r="BK18" t="n">
         <v>326</v>
       </c>
-      <c r="BC18" t="n">
+      <c r="BL18" t="n">
         <v>326</v>
       </c>
-      <c r="BD18" t="n">
+      <c r="BM18" t="n">
         <v>326</v>
       </c>
-      <c r="BE18" t="n">
+      <c r="BN18" t="n">
         <v>326</v>
       </c>
-      <c r="BF18" t="n">
+      <c r="BO18" t="n">
         <v>326</v>
       </c>
-      <c r="BG18" t="n">
+      <c r="BP18" t="n">
         <v>326</v>
       </c>
-      <c r="BH18" t="n">
+      <c r="BQ18" t="n">
         <v>326</v>
       </c>
-      <c r="BI18" t="n">
+      <c r="BR18" t="n">
         <v>326</v>
       </c>
-      <c r="BJ18" t="n">
+      <c r="BS18" t="n">
         <v>326</v>
       </c>
-      <c r="BK18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS18" t="n">
-        <v>669</v>
-      </c>
       <c r="BT18" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB18" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC18" t="n">
         <v>1</v>
       </c>
-      <c r="BU18" t="n">
+      <c r="CD18" t="n">
         <v>0.75</v>
       </c>
-      <c r="BV18" t="n">
+      <c r="CE18" t="n">
         <v>0.95</v>
       </c>
-      <c r="BW18" t="n">
+      <c r="CF18" t="n">
         <v>0.8275862068965517</v>
       </c>
-      <c r="BX18" t="n">
+      <c r="CG18" t="n">
         <v>0.8205128205128205</v>
       </c>
-      <c r="BY18" t="n">
+      <c r="CH18" t="n">
         <v>0.7959183673469388</v>
       </c>
-      <c r="BZ18" t="n">
+      <c r="CI18" t="n">
         <v>0.7288135593220338</v>
       </c>
-      <c r="CA18" t="n">
+      <c r="CJ18" t="n">
         <v>0.75</v>
       </c>
-      <c r="CB18" t="n">
+      <c r="CK18" t="n">
         <v>0.78125</v>
+      </c>
+      <c r="CL18" t="n">
+        <v>499.11</v>
+      </c>
+      <c r="CM18" t="n">
+        <v>83.13</v>
       </c>
     </row>
     <row r="19">
@@ -5022,10 +5638,10 @@
         <v>518</v>
       </c>
       <c r="C19" t="n">
+        <v>88.95478131949592</v>
+      </c>
+      <c r="D19" t="n">
         <v>60</v>
-      </c>
-      <c r="D19" t="n">
-        <v>88.95478131949592</v>
       </c>
       <c r="E19" t="n">
         <v>518</v>
@@ -5034,228 +5650,261 @@
         <v>200</v>
       </c>
       <c r="G19" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="H19" t="inlineStr">
+        <v>83</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="M19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="Q19" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I19" t="n">
-        <v>509.69985467853</v>
-      </c>
-      <c r="J19" t="n">
-        <v>79.35584906657969</v>
-      </c>
-      <c r="K19" t="n">
-        <v>491.8344803682555</v>
-      </c>
-      <c r="L19" t="n">
-        <v>66.86448863803986</v>
-      </c>
-      <c r="M19" t="n">
-        <v>515.4062367310337</v>
-      </c>
-      <c r="N19" t="n">
-        <v>70.50380456396417</v>
-      </c>
-      <c r="O19" t="n">
-        <v>507.2687076710491</v>
-      </c>
-      <c r="P19" t="n">
-        <v>75.26181284488926</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>510.1490500866485</v>
-      </c>
       <c r="R19" t="n">
-        <v>69.9411873722959</v>
+        <v>509.7</v>
       </c>
       <c r="S19" t="n">
-        <v>514.8428550021989</v>
+        <v>79.36</v>
       </c>
       <c r="T19" t="n">
-        <v>69.78697030503875</v>
+        <v>491.83</v>
       </c>
       <c r="U19" t="n">
-        <v>515.8424307642781</v>
+        <v>66.86</v>
       </c>
       <c r="V19" t="n">
-        <v>63.80984683308622</v>
+        <v>515.41</v>
       </c>
       <c r="W19" t="n">
-        <v>514.8367211789669</v>
+        <v>70.5</v>
       </c>
       <c r="X19" t="n">
-        <v>58.26872311121449</v>
+        <v>507.27</v>
       </c>
       <c r="Y19" t="n">
-        <v>515.9297188524245</v>
+        <v>75.26000000000001</v>
       </c>
       <c r="Z19" t="n">
-        <v>58.64055767694343</v>
+        <v>510.15</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>69.94</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>514.84</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>69.79000000000001</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>515.84</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>63.81</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>514.84</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>58.27</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>515.9299999999999</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>58.64</v>
       </c>
       <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
         <v>470.875</v>
       </c>
-      <c r="AK19" t="n">
+      <c r="AT19" t="n">
         <v>479.4</v>
       </c>
-      <c r="AL19" t="n">
+      <c r="AU19" t="n">
         <v>486.6125</v>
       </c>
-      <c r="AM19" t="n">
+      <c r="AV19" t="n">
         <v>491.59</v>
       </c>
-      <c r="AN19" t="n">
+      <c r="AW19" t="n">
         <v>493.9333333333333</v>
       </c>
-      <c r="AO19" t="n">
+      <c r="AX19" t="n">
         <v>495.9714285714286</v>
       </c>
-      <c r="AP19" t="n">
+      <c r="AY19" t="n">
         <v>496.74375</v>
       </c>
-      <c r="AQ19" t="n">
+      <c r="AZ19" t="n">
         <v>497.2444444444445</v>
       </c>
-      <c r="AR19" t="n">
+      <c r="BA19" t="n">
         <v>495.66</v>
       </c>
-      <c r="AS19" t="n">
+      <c r="BB19" t="n">
         <v>115.8881330205988</v>
       </c>
-      <c r="AT19" t="n">
+      <c r="BC19" t="n">
         <v>104.9887613032938</v>
       </c>
-      <c r="AU19" t="n">
+      <c r="BD19" t="n">
         <v>96.91329807487722</v>
       </c>
-      <c r="AV19" t="n">
+      <c r="BE19" t="n">
         <v>92.15325224863201</v>
       </c>
-      <c r="AW19" t="n">
+      <c r="BF19" t="n">
         <v>88.74708758914602</v>
       </c>
-      <c r="AX19" t="n">
+      <c r="BG19" t="n">
         <v>86.00406492528984</v>
       </c>
-      <c r="AY19" t="n">
+      <c r="BH19" t="n">
         <v>84.69240276398764</v>
       </c>
-      <c r="AZ19" t="n">
+      <c r="BI19" t="n">
         <v>82.83857275329211</v>
       </c>
-      <c r="BA19" t="n">
+      <c r="BJ19" t="n">
         <v>81.34577063375821</v>
       </c>
-      <c r="BB19" t="n">
+      <c r="BK19" t="n">
         <v>257</v>
       </c>
-      <c r="BC19" t="n">
+      <c r="BL19" t="n">
         <v>257</v>
       </c>
-      <c r="BD19" t="n">
+      <c r="BM19" t="n">
         <v>257</v>
       </c>
-      <c r="BE19" t="n">
+      <c r="BN19" t="n">
         <v>257</v>
       </c>
-      <c r="BF19" t="n">
+      <c r="BO19" t="n">
         <v>257</v>
       </c>
-      <c r="BG19" t="n">
+      <c r="BP19" t="n">
         <v>257</v>
       </c>
-      <c r="BH19" t="n">
+      <c r="BQ19" t="n">
         <v>257</v>
       </c>
-      <c r="BI19" t="n">
+      <c r="BR19" t="n">
         <v>257</v>
       </c>
-      <c r="BJ19" t="n">
+      <c r="BS19" t="n">
         <v>257</v>
       </c>
-      <c r="BK19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS19" t="n">
-        <v>669</v>
-      </c>
       <c r="BT19" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB19" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC19" t="n">
         <v>0.3</v>
       </c>
-      <c r="BU19" t="n">
+      <c r="CD19" t="n">
         <v>0.35</v>
       </c>
-      <c r="BV19" t="n">
+      <c r="CE19" t="n">
         <v>0.3928571428571428</v>
       </c>
-      <c r="BW19" t="n">
+      <c r="CF19" t="n">
         <v>0.3947368421052632</v>
       </c>
-      <c r="BX19" t="n">
+      <c r="CG19" t="n">
         <v>0.4166666666666667</v>
       </c>
-      <c r="BY19" t="n">
+      <c r="CH19" t="n">
         <v>0.05172413793103448</v>
       </c>
-      <c r="BZ19" t="n">
+      <c r="CI19" t="n">
         <v>0.3088235294117647</v>
       </c>
-      <c r="CA19" t="n">
+      <c r="CJ19" t="n">
         <v>0.3098591549295774</v>
       </c>
-      <c r="CB19" t="n">
+      <c r="CK19" t="n">
         <v>0.3802816901408451</v>
+      </c>
+      <c r="CL19" t="n">
+        <v>515.9299999999999</v>
+      </c>
+      <c r="CM19" t="n">
+        <v>58.64</v>
       </c>
     </row>
     <row r="20">
@@ -5268,10 +5917,10 @@
         <v>522</v>
       </c>
       <c r="C20" t="n">
+        <v>88.95478131949592</v>
+      </c>
+      <c r="D20" t="n">
         <v>60</v>
-      </c>
-      <c r="D20" t="n">
-        <v>88.95478131949592</v>
       </c>
       <c r="E20" t="n">
         <v>522</v>
@@ -5280,228 +5929,261 @@
         <v>200</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H20" t="inlineStr">
+        <v>77</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="M20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="Q20" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I20" t="n">
-        <v>518.6773874071234</v>
-      </c>
-      <c r="J20" t="n">
-        <v>63.82264859407074</v>
-      </c>
-      <c r="K20" t="n">
-        <v>524.9249809350822</v>
-      </c>
-      <c r="L20" t="n">
-        <v>70.13728673754257</v>
-      </c>
-      <c r="M20" t="n">
-        <v>533.6045725979382</v>
-      </c>
-      <c r="N20" t="n">
-        <v>69.15719857485327</v>
-      </c>
-      <c r="O20" t="n">
-        <v>525.0664017470339</v>
-      </c>
-      <c r="P20" t="n">
-        <v>76.60275659054577</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>524.2505672970004</v>
-      </c>
       <c r="R20" t="n">
-        <v>76.24338474295216</v>
+        <v>518.6799999999999</v>
       </c>
       <c r="S20" t="n">
-        <v>515.1040285469427</v>
+        <v>63.82</v>
       </c>
       <c r="T20" t="n">
-        <v>77.46611316006222</v>
+        <v>524.92</v>
       </c>
       <c r="U20" t="n">
-        <v>515.5086905730637</v>
+        <v>70.14</v>
       </c>
       <c r="V20" t="n">
-        <v>75.4546785263516</v>
+        <v>533.6</v>
       </c>
       <c r="W20" t="n">
-        <v>512.8243816850579</v>
+        <v>69.16</v>
       </c>
       <c r="X20" t="n">
-        <v>75.02524543725079</v>
+        <v>525.0700000000001</v>
       </c>
       <c r="Y20" t="n">
-        <v>512.9600369994408</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="Z20" t="n">
-        <v>74.59150441353033</v>
+        <v>524.25</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>76.23999999999999</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>515.1</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>77.47</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>515.51</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>75.45</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>512.8200000000001</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>75.03</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>512.96</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>74.59</v>
       </c>
       <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
         <v>500.65</v>
       </c>
-      <c r="AK20" t="n">
+      <c r="AT20" t="n">
         <v>507.1166666666667</v>
       </c>
-      <c r="AL20" t="n">
+      <c r="AU20" t="n">
         <v>511.6625</v>
       </c>
-      <c r="AM20" t="n">
+      <c r="AV20" t="n">
         <v>514.17</v>
       </c>
-      <c r="AN20" t="n">
+      <c r="AW20" t="n">
         <v>515.0833333333334</v>
       </c>
-      <c r="AO20" t="n">
+      <c r="AX20" t="n">
         <v>514.7142857142857</v>
       </c>
-      <c r="AP20" t="n">
+      <c r="AY20" t="n">
         <v>515.13125</v>
       </c>
-      <c r="AQ20" t="n">
+      <c r="AZ20" t="n">
         <v>514.4666666666667</v>
       </c>
-      <c r="AR20" t="n">
+      <c r="BA20" t="n">
         <v>512.955</v>
       </c>
-      <c r="AS20" t="n">
+      <c r="BB20" t="n">
         <v>86.39084152848611</v>
       </c>
-      <c r="AT20" t="n">
+      <c r="BC20" t="n">
         <v>83.41564434937983</v>
       </c>
-      <c r="AU20" t="n">
+      <c r="BD20" t="n">
         <v>81.95744989779757</v>
       </c>
-      <c r="AV20" t="n">
+      <c r="BE20" t="n">
         <v>80.91675413658163</v>
       </c>
-      <c r="AW20" t="n">
+      <c r="BF20" t="n">
         <v>80.88897569439787</v>
       </c>
-      <c r="AX20" t="n">
+      <c r="BG20" t="n">
         <v>80.43447073010832</v>
       </c>
-      <c r="AY20" t="n">
+      <c r="BH20" t="n">
         <v>79.26420392230972</v>
       </c>
-      <c r="AZ20" t="n">
+      <c r="BI20" t="n">
         <v>78.00116808242183</v>
       </c>
-      <c r="BA20" t="n">
+      <c r="BJ20" t="n">
         <v>77.0231327264738</v>
       </c>
-      <c r="BB20" t="n">
+      <c r="BK20" t="n">
         <v>334</v>
       </c>
-      <c r="BC20" t="n">
+      <c r="BL20" t="n">
         <v>334</v>
       </c>
-      <c r="BD20" t="n">
+      <c r="BM20" t="n">
         <v>334</v>
       </c>
-      <c r="BE20" t="n">
+      <c r="BN20" t="n">
         <v>334</v>
       </c>
-      <c r="BF20" t="n">
+      <c r="BO20" t="n">
         <v>334</v>
       </c>
-      <c r="BG20" t="n">
+      <c r="BP20" t="n">
         <v>334</v>
       </c>
-      <c r="BH20" t="n">
+      <c r="BQ20" t="n">
         <v>334</v>
       </c>
-      <c r="BI20" t="n">
+      <c r="BR20" t="n">
         <v>334</v>
       </c>
-      <c r="BJ20" t="n">
+      <c r="BS20" t="n">
         <v>334</v>
       </c>
-      <c r="BK20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS20" t="n">
-        <v>669</v>
-      </c>
       <c r="BT20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ20" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA20" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB20" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC20" t="n">
         <v>0.5454545454545454</v>
       </c>
-      <c r="BU20" t="n">
+      <c r="CD20" t="n">
         <v>1</v>
       </c>
-      <c r="BV20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW20" t="n">
+      <c r="CE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF20" t="n">
         <v>0.92</v>
       </c>
-      <c r="BX20" t="n">
+      <c r="CG20" t="n">
         <v>0.875</v>
       </c>
-      <c r="BY20" t="n">
+      <c r="CH20" t="n">
         <v>0.8205128205128205</v>
       </c>
-      <c r="BZ20" t="n">
+      <c r="CI20" t="n">
         <v>0.9</v>
       </c>
-      <c r="CA20" t="n">
+      <c r="CJ20" t="n">
         <v>0.975609756097561</v>
       </c>
-      <c r="CB20" t="n">
+      <c r="CK20" t="n">
         <v>0.8695652173913043</v>
+      </c>
+      <c r="CL20" t="n">
+        <v>512.96</v>
+      </c>
+      <c r="CM20" t="n">
+        <v>74.59</v>
       </c>
     </row>
     <row r="21">
@@ -5514,10 +6196,10 @@
         <v>521</v>
       </c>
       <c r="C21" t="n">
+        <v>91.91994069681246</v>
+      </c>
+      <c r="D21" t="n">
         <v>62</v>
-      </c>
-      <c r="D21" t="n">
-        <v>91.91994069681246</v>
       </c>
       <c r="E21" t="n">
         <v>521</v>
@@ -5526,228 +6208,261 @@
         <v>200</v>
       </c>
       <c r="G21" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="H21" t="inlineStr">
+        <v>79.5</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="M21" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="Q21" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I21" t="n">
-        <v>504.1298911257841</v>
-      </c>
-      <c r="J21" t="n">
-        <v>47.368264736821</v>
-      </c>
-      <c r="K21" t="n">
-        <v>519.4010016094064</v>
-      </c>
-      <c r="L21" t="n">
-        <v>61.88254624540121</v>
-      </c>
-      <c r="M21" t="n">
-        <v>511.8358106588339</v>
-      </c>
-      <c r="N21" t="n">
-        <v>85.18971618407716</v>
-      </c>
-      <c r="O21" t="n">
-        <v>518.7731458518572</v>
-      </c>
-      <c r="P21" t="n">
-        <v>75.8665273880567</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>516.534673032388</v>
-      </c>
       <c r="R21" t="n">
-        <v>68.38434825897639</v>
+        <v>504.13</v>
       </c>
       <c r="S21" t="n">
-        <v>520.1168726724743</v>
+        <v>47.37</v>
       </c>
       <c r="T21" t="n">
-        <v>67.59007683962845</v>
+        <v>519.4</v>
       </c>
       <c r="U21" t="n">
-        <v>520.3637254262638</v>
+        <v>61.88</v>
       </c>
       <c r="V21" t="n">
-        <v>65.16942986819173</v>
+        <v>511.84</v>
       </c>
       <c r="W21" t="n">
-        <v>516.9209989090926</v>
+        <v>85.19</v>
       </c>
       <c r="X21" t="n">
-        <v>62.26702148490574</v>
+        <v>518.77</v>
       </c>
       <c r="Y21" t="n">
-        <v>517.6865926663722</v>
+        <v>75.87</v>
       </c>
       <c r="Z21" t="n">
-        <v>62.79036989764571</v>
+        <v>516.53</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>68.38</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>520.12</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>67.59</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>520.36</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>65.17</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>516.92</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>62.27</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>517.6900000000001</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>62.79</v>
       </c>
       <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
         <v>514.55</v>
       </c>
-      <c r="AK21" t="n">
+      <c r="AT21" t="n">
         <v>514.7833333333333</v>
       </c>
-      <c r="AL21" t="n">
+      <c r="AU21" t="n">
         <v>516.4125</v>
       </c>
-      <c r="AM21" t="n">
+      <c r="AV21" t="n">
         <v>515.26</v>
       </c>
-      <c r="AN21" t="n">
+      <c r="AW21" t="n">
         <v>513.8166666666667</v>
       </c>
-      <c r="AO21" t="n">
+      <c r="AX21" t="n">
         <v>513.4928571428571</v>
       </c>
-      <c r="AP21" t="n">
+      <c r="AY21" t="n">
         <v>514.94375</v>
       </c>
-      <c r="AQ21" t="n">
+      <c r="AZ21" t="n">
         <v>514.3277777777778</v>
       </c>
-      <c r="AR21" t="n">
+      <c r="BA21" t="n">
         <v>514.335</v>
       </c>
-      <c r="AS21" t="n">
+      <c r="BB21" t="n">
         <v>93.84054294386836</v>
       </c>
-      <c r="AT21" t="n">
+      <c r="BC21" t="n">
         <v>83.58011957929283</v>
       </c>
-      <c r="AU21" t="n">
+      <c r="BD21" t="n">
         <v>81.72036064378325</v>
       </c>
-      <c r="AV21" t="n">
+      <c r="BE21" t="n">
         <v>84.02471303134571</v>
       </c>
-      <c r="AW21" t="n">
+      <c r="BF21" t="n">
         <v>82.45766422164097</v>
       </c>
-      <c r="AX21" t="n">
+      <c r="BG21" t="n">
         <v>80.61703971144522</v>
       </c>
-      <c r="AY21" t="n">
+      <c r="BH21" t="n">
         <v>80.24643659339335</v>
       </c>
-      <c r="AZ21" t="n">
+      <c r="BI21" t="n">
         <v>77.67974357403862</v>
       </c>
-      <c r="BA21" t="n">
+      <c r="BJ21" t="n">
         <v>77.01118603813346</v>
       </c>
-      <c r="BB21" t="n">
+      <c r="BK21" t="n">
         <v>341</v>
       </c>
-      <c r="BC21" t="n">
+      <c r="BL21" t="n">
         <v>341</v>
       </c>
-      <c r="BD21" t="n">
+      <c r="BM21" t="n">
         <v>341</v>
       </c>
-      <c r="BE21" t="n">
+      <c r="BN21" t="n">
         <v>341</v>
       </c>
-      <c r="BF21" t="n">
+      <c r="BO21" t="n">
         <v>341</v>
       </c>
-      <c r="BG21" t="n">
+      <c r="BP21" t="n">
         <v>341</v>
       </c>
-      <c r="BH21" t="n">
+      <c r="BQ21" t="n">
         <v>341</v>
       </c>
-      <c r="BI21" t="n">
+      <c r="BR21" t="n">
         <v>341</v>
       </c>
-      <c r="BJ21" t="n">
+      <c r="BS21" t="n">
         <v>341</v>
       </c>
-      <c r="BK21" t="n">
+      <c r="BT21" t="n">
         <v>675</v>
       </c>
-      <c r="BL21" t="n">
+      <c r="BU21" t="n">
         <v>675</v>
       </c>
-      <c r="BM21" t="n">
+      <c r="BV21" t="n">
         <v>675</v>
       </c>
-      <c r="BN21" t="n">
+      <c r="BW21" t="n">
         <v>675</v>
       </c>
-      <c r="BO21" t="n">
+      <c r="BX21" t="n">
         <v>675</v>
       </c>
-      <c r="BP21" t="n">
+      <c r="BY21" t="n">
         <v>675</v>
       </c>
-      <c r="BQ21" t="n">
+      <c r="BZ21" t="n">
         <v>675</v>
       </c>
-      <c r="BR21" t="n">
+      <c r="CA21" t="n">
         <v>675</v>
       </c>
-      <c r="BS21" t="n">
+      <c r="CB21" t="n">
         <v>675</v>
       </c>
-      <c r="BT21" t="n">
+      <c r="CC21" t="n">
         <v>0.4</v>
       </c>
-      <c r="BU21" t="n">
+      <c r="CD21" t="n">
         <v>0.875</v>
       </c>
-      <c r="BV21" t="n">
+      <c r="CE21" t="n">
         <v>0.8181818181818182</v>
       </c>
-      <c r="BW21" t="n">
+      <c r="CF21" t="n">
         <v>0.9166666666666666</v>
       </c>
-      <c r="BX21" t="n">
+      <c r="CG21" t="n">
         <v>0.9333333333333333</v>
       </c>
-      <c r="BY21" t="n">
+      <c r="CH21" t="n">
         <v>0.7777777777777778</v>
       </c>
-      <c r="BZ21" t="n">
+      <c r="CI21" t="n">
         <v>0.8421052631578947</v>
       </c>
-      <c r="CA21" t="n">
+      <c r="CJ21" t="n">
         <v>1</v>
       </c>
-      <c r="CB21" t="n">
+      <c r="CK21" t="n">
         <v>0.8846153846153846</v>
+      </c>
+      <c r="CL21" t="n">
+        <v>517.6900000000001</v>
+      </c>
+      <c r="CM21" t="n">
+        <v>62.79</v>
       </c>
     </row>
     <row r="22">
@@ -5760,10 +6475,10 @@
         <v>519.85</v>
       </c>
       <c r="C22" t="n">
+        <v>89.25129725722758</v>
+      </c>
+      <c r="D22" t="n">
         <v>60.2</v>
-      </c>
-      <c r="D22" t="n">
-        <v>89.25129725722758</v>
       </c>
       <c r="E22" t="n">
         <v>519.85</v>
@@ -5772,224 +6487,239 @@
         <v>200</v>
       </c>
       <c r="G22" t="n">
-        <v>0.4809999999999999</v>
-      </c>
-      <c r="H22" t="inlineStr"/>
+        <v>79.7</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.3505</v>
+      </c>
       <c r="I22" t="n">
-        <v>522.5743932457856</v>
+        <v>2.359</v>
       </c>
       <c r="J22" t="n">
-        <v>70.94889758386269</v>
+        <v>2.414</v>
       </c>
       <c r="K22" t="n">
-        <v>519.4490643057864</v>
+        <v>2.4675</v>
       </c>
       <c r="L22" t="n">
-        <v>71.93250126005179</v>
+        <v>2.5195</v>
       </c>
       <c r="M22" t="n">
-        <v>523.7495945265167</v>
+        <v>2.5545</v>
       </c>
       <c r="N22" t="n">
-        <v>73.73514528728901</v>
+        <v>2.5315</v>
       </c>
       <c r="O22" t="n">
-        <v>522.2475598518993</v>
+        <v>2.407999999999999</v>
       </c>
       <c r="P22" t="n">
-        <v>75.1352966873977</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>522.3377229576869</v>
-      </c>
+        <v>2.3685</v>
+      </c>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="n">
-        <v>75.2795536313258</v>
+        <v>522.5744999999999</v>
       </c>
       <c r="S22" t="n">
-        <v>522.0857303287754</v>
+        <v>70.9485</v>
       </c>
       <c r="T22" t="n">
-        <v>73.79659222076833</v>
+        <v>519.449</v>
       </c>
       <c r="U22" t="n">
-        <v>522.520608314003</v>
+        <v>71.932</v>
       </c>
       <c r="V22" t="n">
-        <v>72.68099721525152</v>
+        <v>523.75</v>
       </c>
       <c r="W22" t="n">
-        <v>521.3413796383331</v>
+        <v>73.73550000000002</v>
       </c>
       <c r="X22" t="n">
-        <v>71.75352399873854</v>
+        <v>522.2475000000001</v>
       </c>
       <c r="Y22" t="n">
-        <v>521.6095437358879</v>
+        <v>75.13499999999999</v>
       </c>
       <c r="Z22" t="n">
-        <v>71.53052562768659</v>
+        <v>522.3375</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>75.28</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>522.086</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>73.79799999999999</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>522.5210000000001</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>72.68050000000001</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>521.3410000000001</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>71.7535</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>521.6090000000002</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>71.53099999999999</v>
       </c>
       <c r="AJ22" t="n">
-        <v>513.55</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>515.0941666666665</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>516.225</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>513.5504999999999</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>515.0939999999999</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>516.2239999999999</v>
+      </c>
+      <c r="AV22" t="n">
         <v>517.016</v>
       </c>
-      <c r="AN22" t="n">
-        <v>517.0420833333334</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>516.6053571428572</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>516.4021875</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>515.9608333333334</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>515.3095000000001</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>104.9132531865167</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>97.52060822324091</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>93.51879542171973</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>90.87373687675441</v>
-      </c>
       <c r="AW22" t="n">
-        <v>89.11273260864324</v>
+        <v>517.0425000000001</v>
       </c>
       <c r="AX22" t="n">
-        <v>87.75268435427782</v>
+        <v>516.6044999999999</v>
       </c>
       <c r="AY22" t="n">
-        <v>86.57174887991242</v>
+        <v>516.4019999999999</v>
       </c>
       <c r="AZ22" t="n">
-        <v>85.34006287912328</v>
+        <v>515.961</v>
       </c>
       <c r="BA22" t="n">
-        <v>84.5321122734877</v>
+        <v>515.3100000000001</v>
       </c>
       <c r="BB22" t="n">
+        <v>104.914</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>97.521</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>93.51900000000001</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>90.8725</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>89.11499999999999</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>87.75250000000001</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>86.57249999999999</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>85.34049999999999</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>84.5325</v>
+      </c>
+      <c r="BK22" t="n">
         <v>328.55</v>
       </c>
-      <c r="BC22" t="n">
+      <c r="BL22" t="n">
         <v>328.55</v>
       </c>
-      <c r="BD22" t="n">
+      <c r="BM22" t="n">
         <v>328.55</v>
       </c>
-      <c r="BE22" t="n">
+      <c r="BN22" t="n">
         <v>328.55</v>
       </c>
-      <c r="BF22" t="n">
+      <c r="BO22" t="n">
         <v>328.55</v>
       </c>
-      <c r="BG22" t="n">
+      <c r="BP22" t="n">
         <v>328.55</v>
       </c>
-      <c r="BH22" t="n">
+      <c r="BQ22" t="n">
         <v>328.55</v>
       </c>
-      <c r="BI22" t="n">
+      <c r="BR22" t="n">
         <v>328.55</v>
       </c>
-      <c r="BJ22" t="n">
+      <c r="BS22" t="n">
         <v>328.55</v>
       </c>
-      <c r="BK22" t="n">
+      <c r="BT22" t="n">
         <v>684.75</v>
       </c>
-      <c r="BL22" t="n">
+      <c r="BU22" t="n">
         <v>684.75</v>
       </c>
-      <c r="BM22" t="n">
+      <c r="BV22" t="n">
         <v>684.75</v>
       </c>
-      <c r="BN22" t="n">
+      <c r="BW22" t="n">
         <v>684.75</v>
       </c>
-      <c r="BO22" t="n">
+      <c r="BX22" t="n">
         <v>684.75</v>
       </c>
-      <c r="BP22" t="n">
+      <c r="BY22" t="n">
         <v>684.75</v>
       </c>
-      <c r="BQ22" t="n">
+      <c r="BZ22" t="n">
         <v>684.75</v>
       </c>
-      <c r="BR22" t="n">
+      <c r="CA22" t="n">
         <v>684.75</v>
       </c>
-      <c r="BS22" t="n">
+      <c r="CB22" t="n">
         <v>684.75</v>
       </c>
-      <c r="BT22" t="n">
-        <v>0.5893118686868688</v>
-      </c>
-      <c r="BU22" t="n">
-        <v>0.7062750484809308</v>
-      </c>
-      <c r="BV22" t="n">
-        <v>0.6712582340336271</v>
-      </c>
-      <c r="BW22" t="n">
-        <v>0.714952298733623</v>
-      </c>
-      <c r="BX22" t="n">
-        <v>0.62090705374398</v>
-      </c>
-      <c r="BY22" t="n">
-        <v>0.6865171283789416</v>
-      </c>
-      <c r="BZ22" t="n">
-        <v>0.6901262960161197</v>
-      </c>
-      <c r="CA22" t="n">
-        <v>0.7244957322655671</v>
-      </c>
-      <c r="CB22" t="n">
-        <v>0.6898817953162506</v>
+      <c r="CC22" t="inlineStr"/>
+      <c r="CD22" t="inlineStr"/>
+      <c r="CE22" t="inlineStr"/>
+      <c r="CF22" t="inlineStr"/>
+      <c r="CG22" t="inlineStr"/>
+      <c r="CH22" t="inlineStr"/>
+      <c r="CI22" t="inlineStr"/>
+      <c r="CJ22" t="inlineStr"/>
+      <c r="CK22" t="inlineStr"/>
+      <c r="CL22" t="n">
+        <v>521.6090000000002</v>
+      </c>
+      <c r="CM22" t="n">
+        <v>71.53099999999999</v>
       </c>
     </row>
     <row r="23">
@@ -6002,10 +6732,10 @@
         <v>1.348488432516786</v>
       </c>
       <c r="C23" t="n">
+        <v>1.899846628664752</v>
+      </c>
+      <c r="D23" t="n">
         <v>1.281446551034375</v>
-      </c>
-      <c r="D23" t="n">
-        <v>1.899846628664752</v>
       </c>
       <c r="E23" t="n">
         <v>1.348488432516786</v>
@@ -6014,224 +6744,239 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.01706026469838459</v>
-      </c>
-      <c r="H23" t="inlineStr"/>
+        <v>2.009189414978876</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.275212358198652</v>
+      </c>
       <c r="I23" t="n">
-        <v>33.12246046809412</v>
+        <v>0.2864648412338902</v>
       </c>
       <c r="J23" t="n">
-        <v>16.37701037112957</v>
+        <v>0.287757207600984</v>
       </c>
       <c r="K23" t="n">
-        <v>23.62088477838084</v>
+        <v>0.3050776432665177</v>
       </c>
       <c r="L23" t="n">
-        <v>14.25686904017362</v>
+        <v>0.3431046334191426</v>
       </c>
       <c r="M23" t="n">
-        <v>22.94997052415219</v>
+        <v>0.356303758640086</v>
       </c>
       <c r="N23" t="n">
-        <v>13.1353409234157</v>
+        <v>0.3443418588982085</v>
       </c>
       <c r="O23" t="n">
-        <v>17.78571078760674</v>
+        <v>0.3371334266554135</v>
       </c>
       <c r="P23" t="n">
-        <v>12.10146901864777</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>15.24291470379375</v>
-      </c>
+        <v>0.3091971777633847</v>
+      </c>
+      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="n">
-        <v>11.80885599645721</v>
+        <v>33.1221664488173</v>
       </c>
       <c r="S23" t="n">
-        <v>12.32689253842259</v>
+        <v>16.37768580625545</v>
       </c>
       <c r="T23" t="n">
-        <v>9.803906465928206</v>
+        <v>23.62099376224019</v>
       </c>
       <c r="U23" t="n">
-        <v>10.49685811003188</v>
+        <v>14.25712217214887</v>
       </c>
       <c r="V23" t="n">
-        <v>9.427367181268503</v>
+        <v>22.94890342524132</v>
       </c>
       <c r="W23" t="n">
-        <v>10.39605420260018</v>
+        <v>13.13547085085587</v>
       </c>
       <c r="X23" t="n">
-        <v>8.760884419714779</v>
+        <v>17.78539077445306</v>
       </c>
       <c r="Y23" t="n">
-        <v>9.839125664793102</v>
+        <v>12.10195960643521</v>
       </c>
       <c r="Z23" t="n">
-        <v>9.058939532711268</v>
+        <v>15.24247350938195</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>11.80951890815647</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>12.32641724530138</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>9.802582688680623</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>10.49760819876303</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>9.427577394342398</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>10.39652973478726</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>8.760739739854944</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>9.838733283892747</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>9.059056474629481</v>
       </c>
       <c r="AJ23" t="n">
-        <v>24.05250424646705</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>24.16836610782031</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>22.82545756732808</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>24.05247169156808</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>24.16844319181088</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>22.82540583601849</v>
+      </c>
+      <c r="AV23" t="n">
         <v>21.19638484568337</v>
       </c>
-      <c r="AN23" t="n">
-        <v>19.4637443122722</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>17.1607412782525</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>14.9976633699516</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>13.17668561431242</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>11.91794168249569</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>15.69755238453094</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>14.70219628308917</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>14.17165779295288</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>12.94621651922042</v>
-      </c>
       <c r="AW23" t="n">
-        <v>11.86295533543542</v>
+        <v>19.46291233548944</v>
       </c>
       <c r="AX23" t="n">
-        <v>10.83180776454376</v>
+        <v>17.16027403627343</v>
       </c>
       <c r="AY23" t="n">
-        <v>9.668686154567997</v>
+        <v>14.99918860963382</v>
       </c>
       <c r="AZ23" t="n">
-        <v>8.655847359576081</v>
+        <v>13.17706376525834</v>
       </c>
       <c r="BA23" t="n">
-        <v>8.484148506260517</v>
+        <v>11.9161142553841</v>
       </c>
       <c r="BB23" t="n">
+        <v>15.69765098082479</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>14.70282962382984</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>14.17149321701845</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>12.94746098865069</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>11.86243806483748</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>10.83240211247329</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>9.668130976509749</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>8.656056276570636</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>8.484373794465361</v>
+      </c>
+      <c r="BK23" t="n">
         <v>18.58826738054212</v>
       </c>
-      <c r="BC23" t="n">
+      <c r="BL23" t="n">
         <v>18.58826738054212</v>
       </c>
-      <c r="BD23" t="n">
+      <c r="BM23" t="n">
         <v>18.58826738054212</v>
       </c>
-      <c r="BE23" t="n">
+      <c r="BN23" t="n">
         <v>18.58826738054212</v>
       </c>
-      <c r="BF23" t="n">
+      <c r="BO23" t="n">
         <v>18.58826738054212</v>
       </c>
-      <c r="BG23" t="n">
+      <c r="BP23" t="n">
         <v>18.58826738054212</v>
       </c>
-      <c r="BH23" t="n">
+      <c r="BQ23" t="n">
         <v>18.58826738054212</v>
       </c>
-      <c r="BI23" t="n">
+      <c r="BR23" t="n">
         <v>18.58826738054212</v>
       </c>
-      <c r="BJ23" t="n">
+      <c r="BS23" t="n">
         <v>18.58826738054212</v>
       </c>
-      <c r="BK23" t="n">
+      <c r="BT23" t="n">
         <v>22.71997729798717</v>
       </c>
-      <c r="BL23" t="n">
+      <c r="BU23" t="n">
         <v>22.71997729798717</v>
       </c>
-      <c r="BM23" t="n">
+      <c r="BV23" t="n">
         <v>22.71997729798717</v>
       </c>
-      <c r="BN23" t="n">
+      <c r="BW23" t="n">
         <v>22.71997729798717</v>
       </c>
-      <c r="BO23" t="n">
+      <c r="BX23" t="n">
         <v>22.71997729798717</v>
       </c>
-      <c r="BP23" t="n">
+      <c r="BY23" t="n">
         <v>22.71997729798717</v>
       </c>
-      <c r="BQ23" t="n">
+      <c r="BZ23" t="n">
         <v>22.71997729798717</v>
       </c>
-      <c r="BR23" t="n">
+      <c r="CA23" t="n">
         <v>22.71997729798717</v>
       </c>
-      <c r="BS23" t="n">
+      <c r="CB23" t="n">
         <v>22.71997729798717</v>
       </c>
-      <c r="BT23" t="n">
-        <v>0.2709258752761659</v>
-      </c>
-      <c r="BU23" t="n">
-        <v>0.2303304906311696</v>
-      </c>
-      <c r="BV23" t="n">
-        <v>0.2188010542667076</v>
-      </c>
-      <c r="BW23" t="n">
-        <v>0.1950552841875479</v>
-      </c>
-      <c r="BX23" t="n">
-        <v>0.2643797969658824</v>
-      </c>
-      <c r="BY23" t="n">
-        <v>0.1916094228794683</v>
-      </c>
-      <c r="BZ23" t="n">
-        <v>0.1630451264520648</v>
-      </c>
-      <c r="CA23" t="n">
-        <v>0.2040739007196214</v>
-      </c>
-      <c r="CB23" t="n">
-        <v>0.1698145415387228</v>
+      <c r="CC23" t="inlineStr"/>
+      <c r="CD23" t="inlineStr"/>
+      <c r="CE23" t="inlineStr"/>
+      <c r="CF23" t="inlineStr"/>
+      <c r="CG23" t="inlineStr"/>
+      <c r="CH23" t="inlineStr"/>
+      <c r="CI23" t="inlineStr"/>
+      <c r="CJ23" t="inlineStr"/>
+      <c r="CK23" t="inlineStr"/>
+      <c r="CL23" t="n">
+        <v>9.838733283892747</v>
+      </c>
+      <c r="CM23" t="n">
+        <v>9.059056474629481</v>
       </c>
     </row>
   </sheetData>
